--- a/data/data_electronic_electrostatic_lumo_regression.xlsx
+++ b/data/data_electronic_electrostatic_lumo_regression.xlsx
@@ -73,16 +73,16 @@
     <t>ULSAJQMHTGKPIY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-2.56793573893182</t>
+    <t>-2.567935738931866</t>
   </si>
   <si>
     <t>NAN</t>
   </si>
   <si>
-    <t>-2.205841503277518</t>
-  </si>
-  <si>
-    <t>0.39528879074672263</t>
+    <t>-2.205841503277629</t>
+  </si>
+  <si>
+    <t>0.3952887907466116</t>
   </si>
   <si>
     <t>A12</t>
@@ -97,13 +97,13 @@
     <t>KZJRKRQSDZGHEC-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-2.3364085688280296</t>
-  </si>
-  <si>
-    <t>-2.7685652232517475</t>
-  </si>
-  <si>
-    <t>-0.4419037483442252</t>
+    <t>-2.3364085688280287</t>
+  </si>
+  <si>
+    <t>-2.768565223251712</t>
+  </si>
+  <si>
+    <t>-0.44190374834418966</t>
   </si>
   <si>
     <t>D10</t>
@@ -118,13 +118,13 @@
     <t>PXQMSTLNSHMSJB-LBPDFUHNSA-N</t>
   </si>
   <si>
-    <t>-1.8588247830658577</t>
-  </si>
-  <si>
-    <t>-1.6142635820485487</t>
-  </si>
-  <si>
-    <t>0.4876994428116954</t>
+    <t>-1.8588247830658737</t>
+  </si>
+  <si>
+    <t>-1.6142635820485345</t>
+  </si>
+  <si>
+    <t>0.4876994428117096</t>
   </si>
   <si>
     <t>B5</t>
@@ -139,13 +139,13 @@
     <t>UMJJFEIKYGFCAT-HOSYLAQJSA-N</t>
   </si>
   <si>
-    <t>-2.0580350157728375</t>
-  </si>
-  <si>
-    <t>-1.4743617950799237</t>
-  </si>
-  <si>
-    <t>0.6274262022798638</t>
+    <t>-2.0580350157728544</t>
+  </si>
+  <si>
+    <t>-1.4743617950799548</t>
+  </si>
+  <si>
+    <t>0.6274262022798327</t>
   </si>
   <si>
     <t>D11(trans)</t>
@@ -160,13 +160,13 @@
     <t>YKFKEYKJGVSEIX-KWYDOPHBSA-N</t>
   </si>
   <si>
-    <t>-2.1621734103528505</t>
-  </si>
-  <si>
-    <t>-2.042663929295311</t>
-  </si>
-  <si>
-    <t>0.24147287583685717</t>
+    <t>-2.1621734103528647</t>
+  </si>
+  <si>
+    <t>-2.042663929295295</t>
+  </si>
+  <si>
+    <t>0.24147287583687316</t>
   </si>
   <si>
     <t>D11(cis)</t>
@@ -181,13 +181,13 @@
     <t>YKFKEYKJGVSEIX-BAUXJJEQSA-N</t>
   </si>
   <si>
-    <t>-1.4181238565694692</t>
-  </si>
-  <si>
-    <t>-1.137769816870887</t>
-  </si>
-  <si>
-    <t>0.44317141536073534</t>
+    <t>-1.418123856569454</t>
+  </si>
+  <si>
+    <t>-1.1377698168708665</t>
+  </si>
+  <si>
+    <t>0.44317141536075577</t>
   </si>
   <si>
     <t>A4</t>
@@ -202,13 +202,13 @@
     <t>YQYGPGKTNQNXMH-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-2.131401205591973</t>
-  </si>
-  <si>
-    <t>-2.750244047295297</t>
-  </si>
-  <si>
-    <t>-0.7317966402934464</t>
+    <t>-2.1314012055919624</t>
+  </si>
+  <si>
+    <t>-2.750244047295279</t>
+  </si>
+  <si>
+    <t>-0.7317966402934286</t>
   </si>
   <si>
     <t>D8(cis)</t>
@@ -223,13 +223,13 @@
     <t>UJBOOUHRTQVGRU-ZCFIWIBFSA-N</t>
   </si>
   <si>
-    <t>-2.0996166476156066</t>
-  </si>
-  <si>
-    <t>-2.0993714707400857</t>
-  </si>
-  <si>
-    <t>0.004050387222651608</t>
+    <t>-2.09961664761562</t>
+  </si>
+  <si>
+    <t>-2.099371470740093</t>
+  </si>
+  <si>
+    <t>0.004050387222644503</t>
   </si>
   <si>
     <t>D8(trans)</t>
@@ -247,10 +247,10 @@
     <t>-1.4536067308036387</t>
   </si>
   <si>
-    <t>-1.4327375420983035</t>
-  </si>
-  <si>
-    <t>0.07008154881553841</t>
+    <t>-1.432737542098315</t>
+  </si>
+  <si>
+    <t>0.07008154881552686</t>
   </si>
   <si>
     <t>C3</t>
@@ -265,13 +265,13 @@
     <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.8253076512992399</t>
-  </si>
-  <si>
-    <t>-2.2683308690106667</t>
-  </si>
-  <si>
-    <t>-0.4617106037434684</t>
+    <t>-1.8253076512992337</t>
+  </si>
+  <si>
+    <t>-2.2683308690106934</t>
+  </si>
+  <si>
+    <t>-0.46171060374349504</t>
   </si>
   <si>
     <t>A9</t>
@@ -286,13 +286,13 @@
     <t>ARKIFHPFTHVKDT-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.6949259275263149</t>
-  </si>
-  <si>
-    <t>-1.0657445375005565</t>
-  </si>
-  <si>
-    <t>0.7293108110596251</t>
+    <t>-1.694925927526369</t>
+  </si>
+  <si>
+    <t>-1.065744537500513</t>
+  </si>
+  <si>
+    <t>0.7293108110596687</t>
   </si>
   <si>
     <t>B6</t>
@@ -307,13 +307,13 @@
     <t>KCKZIWSINLBROE-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.7358257274783142</t>
-  </si>
-  <si>
-    <t>-2.130936886682285</t>
-  </si>
-  <si>
-    <t>-0.4053709404651944</t>
+    <t>-1.7358257274782956</t>
+  </si>
+  <si>
+    <t>-2.1309368866822895</t>
+  </si>
+  <si>
+    <t>-0.40537094046519884</t>
   </si>
   <si>
     <t>D9(trans)</t>
@@ -328,13 +328,13 @@
     <t>VGVHNLRUAMRIEW-NFPUQWBCSA-N</t>
   </si>
   <si>
-    <t>-2.4677645801465813</t>
-  </si>
-  <si>
-    <t>-2.4140493211831755</t>
-  </si>
-  <si>
-    <t>0.11755895798171512</t>
+    <t>-2.467764580146606</t>
+  </si>
+  <si>
+    <t>-2.4140493211831675</t>
+  </si>
+  <si>
+    <t>0.11755895798172311</t>
   </si>
   <si>
     <t>D9(cis)</t>
@@ -349,13 +349,13 @@
     <t>VGVHNLRUAMRIEW-TXNNBAIQSA-N</t>
   </si>
   <si>
-    <t>-1.8167861350749401</t>
-  </si>
-  <si>
-    <t>-1.8831826207393245</t>
-  </si>
-  <si>
-    <t>-0.15458276642278101</t>
+    <t>-1.8167861350749428</t>
+  </si>
+  <si>
+    <t>-1.88318262073932</t>
+  </si>
+  <si>
+    <t>-0.15458276642277657</t>
   </si>
   <si>
     <t>D4</t>
@@ -370,13 +370,13 @@
     <t>JHIVVAPYMSGYDF-AZXPZELESA-N</t>
   </si>
   <si>
-    <t>-2.1075605836911766</t>
-  </si>
-  <si>
-    <t>-2.1138431188447804</t>
-  </si>
-  <si>
-    <t>-0.030289639680924907</t>
+    <t>-2.1075605836911784</t>
+  </si>
+  <si>
+    <t>-2.1138431188447697</t>
+  </si>
+  <si>
+    <t>-0.03028963968091425</t>
   </si>
   <si>
     <t>B7</t>
@@ -391,13 +391,13 @@
     <t>YLQWCDOCJODRMT-KHWBWMQUSA-N</t>
   </si>
   <si>
-    <t>-1.6970065702510126</t>
-  </si>
-  <si>
-    <t>-0.0034219488445188517</t>
-  </si>
-  <si>
-    <t>1.745897798850042</t>
+    <t>-1.6970065702510215</t>
+  </si>
+  <si>
+    <t>-0.0034219488444682256</t>
+  </si>
+  <si>
+    <t>1.7458977988500926</t>
   </si>
   <si>
     <t>D1(cis)</t>
@@ -412,13 +412,13 @@
     <t>GPPSQLLIFNWNSB-VFOIXEAWSA-N</t>
   </si>
   <si>
-    <t>-1.9959161290248337</t>
-  </si>
-  <si>
-    <t>-3.039085505846616</t>
-  </si>
-  <si>
-    <t>-1.0699591937574786</t>
+    <t>-1.995916129024832</t>
+  </si>
+  <si>
+    <t>-3.0390855058466637</t>
+  </si>
+  <si>
+    <t>-1.0699591937575261</t>
   </si>
   <si>
     <t>D1(trans)</t>
@@ -433,13 +433,13 @@
     <t>GPPSQLLIFNWNSB-VXPBIQBCSA-N</t>
   </si>
   <si>
-    <t>-0.9385737631459641</t>
-  </si>
-  <si>
-    <t>-1.8421180457120343</t>
-  </si>
-  <si>
-    <t>-0.9301463403001767</t>
+    <t>-0.938573763145949</t>
+  </si>
+  <si>
+    <t>-1.84211804571199</t>
+  </si>
+  <si>
+    <t>-0.9301463403001323</t>
   </si>
   <si>
     <t>A11</t>
@@ -454,13 +454,13 @@
     <t>ABXGMGUHGLQMAW-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.29781714753637</t>
-  </si>
-  <si>
-    <t>-1.1913075680634826</t>
-  </si>
-  <si>
-    <t>0.39289034136422085</t>
+    <t>-1.2978171475363762</t>
+  </si>
+  <si>
+    <t>-1.1913075680634835</t>
+  </si>
+  <si>
+    <t>0.39289034136421996</t>
   </si>
   <si>
     <t>E4</t>
@@ -475,13 +475,13 @@
     <t>IYKFYARMMIESOX-VJJZLTLGSA-N</t>
   </si>
   <si>
-    <t>-1.3841170380508796</t>
-  </si>
-  <si>
-    <t>-1.1578799145688778</t>
-  </si>
-  <si>
-    <t>0.3125938687252172</t>
+    <t>-1.3841170380508911</t>
+  </si>
+  <si>
+    <t>-1.1578799145688725</t>
+  </si>
+  <si>
+    <t>0.31259386872522255</t>
   </si>
   <si>
     <t>A6</t>
@@ -496,13 +496,13 @@
     <t>HHAISVSEJFEWBZ-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.372287782685068</t>
-  </si>
-  <si>
-    <t>-1.3102220949604089</t>
-  </si>
-  <si>
-    <t>0.15318300097592097</t>
+    <t>-1.3722877826850794</t>
+  </si>
+  <si>
+    <t>-1.3102220949604169</t>
+  </si>
+  <si>
+    <t>0.15318300097591298</t>
   </si>
   <si>
     <t>C8</t>
@@ -517,13 +517,13 @@
     <t>BANVZEUCJHUPOI-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.3767427137025274</t>
-  </si>
-  <si>
-    <t>-1.966129500523457</t>
-  </si>
-  <si>
-    <t>-0.7816586082618036</t>
+    <t>-1.3767427137025186</t>
+  </si>
+  <si>
+    <t>-1.9661295005234374</t>
+  </si>
+  <si>
+    <t>-0.781658608261784</t>
   </si>
   <si>
     <t>C2</t>
@@ -538,13 +538,13 @@
     <t>AKGGYBADQZYZPD-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.1884970378758588</t>
-  </si>
-  <si>
-    <t>-1.3945621730810345</t>
-  </si>
-  <si>
-    <t>-0.2548113830540104</t>
+    <t>-1.1884970378758535</t>
+  </si>
+  <si>
+    <t>-1.3945621730809723</t>
+  </si>
+  <si>
+    <t>-0.25481138305394824</t>
   </si>
   <si>
     <t>C4</t>
@@ -559,13 +559,13 @@
     <t>PJCCSZUMZMCWSX-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.8474716204066022</t>
-  </si>
-  <si>
-    <t>-0.34090385424916647</t>
-  </si>
-  <si>
-    <t>0.5412036491196821</t>
+    <t>-0.8474716204065853</t>
+  </si>
+  <si>
+    <t>-0.34090385424917</t>
+  </si>
+  <si>
+    <t>0.5412036491196786</t>
   </si>
   <si>
     <t>C6</t>
@@ -580,13 +580,13 @@
     <t>LKENTYLPIUIMFG-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.8463028315210224</t>
-  </si>
-  <si>
-    <t>-0.7778189960365482</t>
-  </si>
-  <si>
-    <t>0.09630613554110756</t>
+    <t>-0.8463028315210197</t>
+  </si>
+  <si>
+    <t>-0.7778189960365518</t>
+  </si>
+  <si>
+    <t>0.09630613554110401</t>
   </si>
   <si>
     <t>B2</t>
@@ -601,13 +601,13 @@
     <t>MEDSHTHCZIOVPU-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.7988953135411831</t>
-  </si>
-  <si>
-    <t>-0.7208740753844252</t>
-  </si>
-  <si>
-    <t>0.09111670111115877</t>
+    <t>-0.7988953135411592</t>
+  </si>
+  <si>
+    <t>-0.7208740753844181</t>
+  </si>
+  <si>
+    <t>0.09111670111116588</t>
   </si>
   <si>
     <t>C5</t>
@@ -622,13 +622,13 @@
     <t>VKCYHJWLYTUGCC-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.9836609609732472</t>
-  </si>
-  <si>
-    <t>-1.1637205552708627</t>
-  </si>
-  <si>
-    <t>-0.36780987861415415</t>
+    <t>-0.9836609609732463</t>
+  </si>
+  <si>
+    <t>-1.1637205552708307</t>
+  </si>
+  <si>
+    <t>-0.3678098786141222</t>
   </si>
   <si>
     <t>D13(trans)</t>
@@ -643,13 +643,13 @@
     <t>POSWICCRDBKBMH-ZETCQYMHSA-N</t>
   </si>
   <si>
-    <t>-1.0525527183470178</t>
-  </si>
-  <si>
-    <t>-0.9085995314375532</t>
-  </si>
-  <si>
-    <t>0.18443326809828475</t>
+    <t>-1.052552718347032</t>
+  </si>
+  <si>
+    <t>-0.908599531437539</t>
+  </si>
+  <si>
+    <t>0.18443326809829896</t>
   </si>
   <si>
     <t>D13(cis)</t>
@@ -664,13 +664,13 @@
     <t>POSWICCRDBKBMH-SSDOTTSWSA-N</t>
   </si>
   <si>
-    <t>-0.1273420140768149</t>
-  </si>
-  <si>
-    <t>0.0006218987464281511</t>
-  </si>
-  <si>
-    <t>0.18423352121578385</t>
+    <t>-0.12734201407681045</t>
+  </si>
+  <si>
+    <t>0.0006218987464245984</t>
+  </si>
+  <si>
+    <t>0.1842335212157803</t>
   </si>
   <si>
     <t>A5</t>
@@ -685,13 +685,13 @@
     <t>BUZYGTVTZYSBCU-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-1.0275950615862808</t>
-  </si>
-  <si>
-    <t>-1.1749411819754307</t>
-  </si>
-  <si>
-    <t>-0.38446757800579157</t>
+    <t>-1.0275950615862826</t>
+  </si>
+  <si>
+    <t>-1.1749411819754272</t>
+  </si>
+  <si>
+    <t>-0.384467578005788</t>
   </si>
   <si>
     <t>A17</t>
@@ -706,13 +706,13 @@
     <t>OECPUBRNDKXFDX-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.7598848115045449</t>
-  </si>
-  <si>
-    <t>-0.7303248914881468</t>
-  </si>
-  <si>
-    <t>0.036944401564300455</t>
+    <t>-0.7598848115045271</t>
+  </si>
+  <si>
+    <t>-0.7303248914881264</t>
+  </si>
+  <si>
+    <t>0.03694440156432088</t>
   </si>
   <si>
     <t>A10</t>
@@ -727,13 +727,13 @@
     <t>UUWJBXKHMMQDED-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.9974763020563753</t>
-  </si>
-  <si>
-    <t>-1.1105102266438314</t>
-  </si>
-  <si>
-    <t>-0.3653996451813485</t>
+    <t>-0.99747630205637</t>
+  </si>
+  <si>
+    <t>-1.1105102266438207</t>
+  </si>
+  <si>
+    <t>-0.36539964518133783</t>
   </si>
   <si>
     <t>B10</t>
@@ -748,13 +748,13 @@
     <t>SNVTZAIYUGUKNI-KCKQSJSWSA-N</t>
   </si>
   <si>
-    <t>-0.4517434261991182</t>
-  </si>
-  <si>
-    <t>-0.13505243161876157</t>
-  </si>
-  <si>
-    <t>0.43569986570904606</t>
+    <t>-0.4517434261990916</t>
+  </si>
+  <si>
+    <t>-0.13505243161875713</t>
+  </si>
+  <si>
+    <t>0.4356998657090505</t>
   </si>
   <si>
     <t>E2(endo)</t>
@@ -769,13 +769,13 @@
     <t>KPMKEVXVVHNIEY-PRJDIBJQSA-N</t>
   </si>
   <si>
-    <t>-0.8844567771783884</t>
-  </si>
-  <si>
-    <t>-0.8237554855084106</t>
-  </si>
-  <si>
-    <t>0.07474907632137162</t>
+    <t>-0.8844567771783742</t>
+  </si>
+  <si>
+    <t>-0.8237554855083191</t>
+  </si>
+  <si>
+    <t>0.0747490763214631</t>
   </si>
   <si>
     <t>E2(exo)</t>
@@ -790,13 +790,13 @@
     <t>KPMKEVXVVHNIEY-GDVGLLTNSA-N</t>
   </si>
   <si>
-    <t>0.585099225416859</t>
-  </si>
-  <si>
-    <t>1.0002521649055112</t>
-  </si>
-  <si>
-    <t>0.4941427645841321</t>
+    <t>0.5850992254168634</t>
+  </si>
+  <si>
+    <t>1.0002521649053966</t>
+  </si>
+  <si>
+    <t>0.4941427645840175</t>
   </si>
   <si>
     <t>D5</t>
@@ -811,13 +811,13 @@
     <t>CGZZMOTZOONQIA-HOSYLAQJSA-N</t>
   </si>
   <si>
-    <t>-0.6309206991730569</t>
-  </si>
-  <si>
-    <t>-0.8381504712971113</t>
-  </si>
-  <si>
-    <t>-0.2963889577020362</t>
+    <t>-0.6309206991730534</t>
+  </si>
+  <si>
+    <t>-0.8381504712971308</t>
+  </si>
+  <si>
+    <t>-0.29638895770205576</t>
   </si>
   <si>
     <t>C7</t>
@@ -832,13 +832,13 @@
     <t>DBNWBEGCONIRGQ-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.3769846667297214</t>
-  </si>
-  <si>
-    <t>0.3892255795321846</t>
-  </si>
-  <si>
-    <t>0.9072948302996106</t>
+    <t>-0.3769846667297072</t>
+  </si>
+  <si>
+    <t>0.3892255795321864</t>
+  </si>
+  <si>
+    <t>0.9072948302996123</t>
   </si>
   <si>
     <t>C1</t>
@@ -853,13 +853,13 @@
     <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.3270888939499743</t>
-  </si>
-  <si>
-    <t>-0.16739500013273556</t>
-  </si>
-  <si>
-    <t>0.3137065602296871</t>
+    <t>-0.3270888939499592</t>
+  </si>
+  <si>
+    <t>-0.16739500013273645</t>
+  </si>
+  <si>
+    <t>0.31370656022968624</t>
   </si>
   <si>
     <t>D3</t>
@@ -874,13 +874,13 @@
     <t>FTGZMZBYOHMEPS-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.35268780417124734</t>
-  </si>
-  <si>
-    <t>0.043175530433839704</t>
-  </si>
-  <si>
-    <t>0.5203975781415563</t>
+    <t>-0.3526878041712491</t>
+  </si>
+  <si>
+    <t>0.04317553043385747</t>
+  </si>
+  <si>
+    <t>0.5203975781415741</t>
   </si>
   <si>
     <t>D12(trans)</t>
@@ -895,13 +895,13 @@
     <t>ZPVOLGVTNLDBFI-SSDOTTSWSA-N</t>
   </si>
   <si>
-    <t>-0.8287624879716233</t>
-  </si>
-  <si>
-    <t>-1.1259876099643007</t>
-  </si>
-  <si>
-    <t>-0.38792868549341974</t>
+    <t>-0.82876248797161</t>
+  </si>
+  <si>
+    <t>-1.1259876099643087</t>
+  </si>
+  <si>
+    <t>-0.38792868549342774</t>
   </si>
   <si>
     <t>D12(cis)</t>
@@ -916,13 +916,13 @@
     <t>ZPVOLGVTNLDBFI-ZETCQYMHSA-N</t>
   </si>
   <si>
-    <t>-0.13324507342312142</t>
-  </si>
-  <si>
-    <t>-0.2631120124475812</t>
-  </si>
-  <si>
-    <t>-0.1440735510044432</t>
+    <t>-0.13324507342312852</t>
+  </si>
+  <si>
+    <t>-0.26311201244760074</t>
+  </si>
+  <si>
+    <t>-0.14407355100446273</t>
   </si>
   <si>
     <t>C9</t>
@@ -937,13 +937,13 @@
     <t>WSGCRAOTEDLMFQ-CDYZYAPPSA-N</t>
   </si>
   <si>
-    <t>-0.10636876490891645</t>
-  </si>
-  <si>
-    <t>-0.0013875704277559464</t>
-  </si>
-  <si>
-    <t>0.27855012291242653</t>
+    <t>-0.10636876490892533</t>
+  </si>
+  <si>
+    <t>-0.0013875704277728218</t>
+  </si>
+  <si>
+    <t>0.27855012291240966</t>
   </si>
   <si>
     <t>D14</t>
@@ -958,13 +958,13 @@
     <t>OQJMHUOCLRCSED-HOSYLAQJSA-N</t>
   </si>
   <si>
-    <t>-0.20416206211070076</t>
-  </si>
-  <si>
-    <t>-0.010497007604589825</t>
-  </si>
-  <si>
-    <t>0.2606307919074445</t>
+    <t>-0.20416206211073717</t>
+  </si>
+  <si>
+    <t>-0.010497007604618247</t>
+  </si>
+  <si>
+    <t>0.26063079190741606</t>
   </si>
   <si>
     <t>A1</t>
@@ -979,13 +979,13 @@
     <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.36745456885189043</t>
-  </si>
-  <si>
-    <t>-0.40167603000593655</t>
-  </si>
-  <si>
-    <t>-0.15031611440667964</t>
+    <t>-0.36745456885189665</t>
+  </si>
+  <si>
+    <t>-0.4016760300059259</t>
+  </si>
+  <si>
+    <t>-0.15031611440666898</t>
   </si>
   <si>
     <t>A15</t>
@@ -1000,13 +1000,13 @@
     <t>BSMGLVDZZMBWQB-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.24437212682499787</t>
-  </si>
-  <si>
-    <t>-0.2589645245446963</t>
-  </si>
-  <si>
-    <t>-0.03351525814465242</t>
+    <t>-0.2443721268250112</t>
+  </si>
+  <si>
+    <t>-0.2589645245446892</t>
+  </si>
+  <si>
+    <t>-0.033515258144645316</t>
   </si>
   <si>
     <t>A7</t>
@@ -1021,13 +1021,13 @@
     <t>FSPSELPMWGWDRY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.1682935820944591</t>
-  </si>
-  <si>
-    <t>-0.15780268281965615</t>
-  </si>
-  <si>
-    <t>0.05284661834857646</t>
+    <t>-0.16829358209446177</t>
+  </si>
+  <si>
+    <t>-0.15780268281964904</t>
+  </si>
+  <si>
+    <t>0.05284661834858356</t>
   </si>
   <si>
     <t>A8</t>
@@ -1042,7 +1042,7 @@
     <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.3208522795807296</t>
+    <t>-0.32085227958073403</t>
   </si>
   <si>
     <t>-0.4177110541811331</t>
@@ -1063,13 +1063,13 @@
     <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.2472319509616332</t>
-  </si>
-  <si>
-    <t>-0.3527263404889682</t>
-  </si>
-  <si>
-    <t>-0.15723706657961792</t>
+    <t>-0.24723195096163497</t>
+  </si>
+  <si>
+    <t>-0.3527263404889611</t>
+  </si>
+  <si>
+    <t>-0.1572370665796108</t>
   </si>
   <si>
     <t>A13</t>
@@ -1084,13 +1084,13 @@
     <t>KRIOVPPHQSLHCZ-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.17211770253281955</t>
-  </si>
-  <si>
-    <t>-0.21325695672804557</t>
-  </si>
-  <si>
-    <t>-0.07319862522429896</t>
+    <t>-0.1721177025328231</t>
+  </si>
+  <si>
+    <t>-0.21325695672805178</t>
+  </si>
+  <si>
+    <t>-0.07319862522430517</t>
   </si>
   <si>
     <t>A19</t>
@@ -1105,13 +1105,13 @@
     <t>MVEBDOSCXOQNAR-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.07844223545098661</t>
-  </si>
-  <si>
-    <t>0.020700210813219933</t>
-  </si>
-  <si>
-    <t>0.11810932189518923</t>
+    <t>-0.07844223545098838</t>
+  </si>
+  <si>
+    <t>0.02070021081317197</t>
+  </si>
+  <si>
+    <t>0.11810932189514127</t>
   </si>
   <si>
     <t>B3</t>
@@ -1126,13 +1126,13 @@
     <t>XHLHPRDBBAGVEG-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>-0.09063698772616924</t>
-  </si>
-  <si>
-    <t>-0.06803895408654359</t>
-  </si>
-  <si>
-    <t>0.025755904712649005</t>
+    <t>-0.09063698772617101</t>
+  </si>
+  <si>
+    <t>-0.06803895408650273</t>
+  </si>
+  <si>
+    <t>0.02575590471268986</t>
   </si>
   <si>
     <t>A22</t>
@@ -1147,13 +1147,13 @@
     <t>BMFYCFSWWDXEPB-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.028661979935248993</t>
-  </si>
-  <si>
-    <t>0.09725340799163273</t>
-  </si>
-  <si>
-    <t>0.15621456716310123</t>
+    <t>0.028661979935247217</t>
+  </si>
+  <si>
+    <t>0.09725340799160698</t>
+  </si>
+  <si>
+    <t>0.15621456716307547</t>
   </si>
   <si>
     <t>A18</t>
@@ -1168,13 +1168,13 @@
     <t>XKGLSKVNOSHTAD-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.10802525662939733</t>
-  </si>
-  <si>
-    <t>0.15634691870606598</t>
-  </si>
-  <si>
-    <t>0.2121793973834644</t>
+    <t>0.1080252566294071</t>
+  </si>
+  <si>
+    <t>0.15634691870607398</t>
+  </si>
+  <si>
+    <t>0.21217939738347238</t>
   </si>
   <si>
     <t>A14</t>
@@ -1192,10 +1192,10 @@
     <t>0.3677425869932964</t>
   </si>
   <si>
-    <t>0.45276690611024506</t>
-  </si>
-  <si>
-    <t>0.5056751175052717</t>
+    <t>0.45276690611025483</t>
+  </si>
+  <si>
+    <t>0.5056751175052815</t>
   </si>
   <si>
     <t>B4</t>
@@ -1210,13 +1210,13 @@
     <t>KWHUHTFXMNQHAA-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.016178774774402882</t>
-  </si>
-  <si>
-    <t>0.09597469982525375</t>
-  </si>
-  <si>
-    <t>0.10929367321167695</t>
+    <t>0.016178774774401994</t>
+  </si>
+  <si>
+    <t>0.0959746998251978</t>
+  </si>
+  <si>
+    <t>0.10929367321162099</t>
   </si>
   <si>
     <t>A23</t>
@@ -1231,10 +1231,10 @@
     <t>RWCCWEUUXYIKHB-KHWBWMQUSA-N</t>
   </si>
   <si>
-    <t>-0.06547260003116495</t>
-  </si>
-  <si>
-    <t>-0.25601347705362</t>
+    <t>-0.0654726000311685</t>
+  </si>
+  <si>
+    <t>-0.2560134770536511</t>
   </si>
   <si>
     <t>A2</t>
@@ -1249,13 +1249,13 @@
     <t>GNKZMNRKLCTJAY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.06829019947906723</t>
-  </si>
-  <si>
-    <t>0.03802366574529703</t>
-  </si>
-  <si>
-    <t>-0.12139143393545668</t>
+    <t>0.06829019947907522</t>
+  </si>
+  <si>
+    <t>0.038023665745294366</t>
+  </si>
+  <si>
+    <t>-0.12139143393545934</t>
   </si>
   <si>
     <t>A21</t>
@@ -1270,13 +1270,13 @@
     <t>VYDIMQRLNMMJBW-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.36849012080229926</t>
-  </si>
-  <si>
-    <t>0.5705664896738649</t>
-  </si>
-  <si>
-    <t>0.402967447019169</t>
+    <t>0.3684901208022957</t>
+  </si>
+  <si>
+    <t>0.5705664896738889</t>
+  </si>
+  <si>
+    <t>0.40296744701919296</t>
   </si>
   <si>
     <t>D15(trans)</t>
@@ -1291,13 +1291,13 @@
     <t>NFLGAXVYCFJBMK-DTWKUNHWSA-N</t>
   </si>
   <si>
-    <t>-0.14919895685186813</t>
-  </si>
-  <si>
-    <t>-0.44727717693516666</t>
-  </si>
-  <si>
-    <t>-0.5452878085889878</t>
+    <t>-0.14919895685186102</t>
+  </si>
+  <si>
+    <t>-0.4472771769351773</t>
+  </si>
+  <si>
+    <t>-0.5452878085889985</t>
   </si>
   <si>
     <t>D15(cis)</t>
@@ -1312,13 +1312,13 @@
     <t>NFLGAXVYCFJBMK-BDAKNGLRSA-N</t>
   </si>
   <si>
-    <t>0.03566897724705509</t>
-  </si>
-  <si>
-    <t>-0.2968148663712489</t>
-  </si>
-  <si>
-    <t>-0.5738216636230968</t>
+    <t>0.035668977247066636</t>
+  </si>
+  <si>
+    <t>-0.29681486637128707</t>
+  </si>
+  <si>
+    <t>-0.573821663623135</t>
   </si>
   <si>
     <t>A16</t>
@@ -1333,13 +1333,13 @@
     <t>PJRHFTYXYCVOSJ-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.15047966010418623</t>
-  </si>
-  <si>
-    <t>-0.08980858213616116</t>
-  </si>
-  <si>
-    <t>-0.3024277072459365</t>
+    <t>0.15047966010418978</t>
+  </si>
+  <si>
+    <t>-0.08980858213612386</t>
+  </si>
+  <si>
+    <t>-0.3024277072458992</t>
   </si>
   <si>
     <t>D6</t>
@@ -1354,13 +1354,13 @@
     <t>IIRFCWANHMSDCG-PTQBSOBMSA-N</t>
   </si>
   <si>
-    <t>0.26629297996724244</t>
-  </si>
-  <si>
-    <t>0.210112310249853</t>
-  </si>
-  <si>
-    <t>-0.06586602916098838</t>
+    <t>0.2662929799672451</t>
+  </si>
+  <si>
+    <t>0.21011231024986632</t>
+  </si>
+  <si>
+    <t>-0.06586602916097506</t>
   </si>
   <si>
     <t>D2(trans)</t>
@@ -1375,13 +1375,13 @@
     <t>CWZGKTMWPFTJCS-SECBINFHSA-N</t>
   </si>
   <si>
-    <t>0.23211665989676344</t>
-  </si>
-  <si>
-    <t>-0.3770872643762049</t>
-  </si>
-  <si>
-    <t>-0.7130353547987844</t>
+    <t>0.23211665989676433</t>
+  </si>
+  <si>
+    <t>-0.37708726437619333</t>
+  </si>
+  <si>
+    <t>-0.7130353547987729</t>
   </si>
   <si>
     <t>D2(cis)</t>
@@ -1396,13 +1396,13 @@
     <t>CWZGKTMWPFTJCS-VIFPVBQESA-N</t>
   </si>
   <si>
-    <t>0.3433736174466162</t>
-  </si>
-  <si>
-    <t>0.0579324012988538</t>
-  </si>
-  <si>
-    <t>-0.3001930540867449</t>
+    <t>0.3433736174466251</t>
+  </si>
+  <si>
+    <t>0.05793240129879873</t>
+  </si>
+  <si>
+    <t>-0.30019305408679997</t>
   </si>
   <si>
     <t>D7</t>
@@ -1417,13 +1417,13 @@
     <t>SXVPOSFURRDKBO-DETAZLGJSA-N</t>
   </si>
   <si>
-    <t>0.46432863780522826</t>
-  </si>
-  <si>
-    <t>0.040305506735057506</t>
-  </si>
-  <si>
-    <t>-0.4693557855961623</t>
+    <t>0.4643286378052265</t>
+  </si>
+  <si>
+    <t>0.04030550673511879</t>
+  </si>
+  <si>
+    <t>-0.469355785596101</t>
   </si>
   <si>
     <t>A3</t>
@@ -1438,13 +1438,13 @@
     <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.2591334132756513</t>
-  </si>
-  <si>
-    <t>0.15032220459770684</t>
-  </si>
-  <si>
-    <t>-0.4102846499702013</t>
+    <t>0.2591334132756442</t>
+  </si>
+  <si>
+    <t>0.1503222045977095</t>
+  </si>
+  <si>
+    <t>-0.41028464997019864</t>
   </si>
   <si>
     <t>A20</t>
@@ -1459,13 +1459,13 @@
     <t>HEOVGVNITGAUKL-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>0.5228081104288353</t>
-  </si>
-  <si>
-    <t>0.48199567812827926</t>
-  </si>
-  <si>
-    <t>-0.08303993921227348</t>
+    <t>0.5228081104288389</t>
+  </si>
+  <si>
+    <t>0.4819956781282828</t>
+  </si>
+  <si>
+    <t>-0.08303993921226993</t>
   </si>
   <si>
     <t>C11</t>
@@ -1480,13 +1480,13 @@
     <t>TWXWPPKDQOWNSX-KHWBWMQUSA-N</t>
   </si>
   <si>
-    <t>0.8062741652322263</t>
-  </si>
-  <si>
-    <t>0.8236573984543796</t>
-  </si>
-  <si>
-    <t>0.02096564397702827</t>
+    <t>0.8062741652322432</t>
+  </si>
+  <si>
+    <t>0.8236573984543805</t>
+  </si>
+  <si>
+    <t>0.020965643977029158</t>
   </si>
   <si>
     <t>B9</t>
@@ -1501,13 +1501,13 @@
     <t>BMVWCPGVLSILMU-KCKQSJSWSA-N</t>
   </si>
   <si>
-    <t>0.95084232411652</t>
-  </si>
-  <si>
-    <t>0.6903939130454178</t>
-  </si>
-  <si>
-    <t>-0.3324033518722844</t>
+    <t>0.9508423241165289</t>
+  </si>
+  <si>
+    <t>0.6903939130454249</t>
+  </si>
+  <si>
+    <t>-0.3324033518722773</t>
   </si>
   <si>
     <t>C10</t>
@@ -1522,13 +1522,13 @@
     <t>PTTPXKJBFFKCEK-HOSYLAQJSA-N</t>
   </si>
   <si>
-    <t>0.39869493438487247</t>
-  </si>
-  <si>
-    <t>0.8384528375647502</t>
-  </si>
-  <si>
-    <t>0.530803961238305</t>
+    <t>0.3986949343848645</t>
+  </si>
+  <si>
+    <t>0.8384528375647653</t>
+  </si>
+  <si>
+    <t>0.5308039612383201</t>
   </si>
   <si>
     <t>B8</t>
@@ -1543,13 +1543,13 @@
     <t>GWFCYDIAPRIMLA-KHWBWMQUSA-N</t>
   </si>
   <si>
-    <t>1.1809515275934448</t>
-  </si>
-  <si>
-    <t>1.2922942753064812</t>
-  </si>
-  <si>
-    <t>0.13550423546468116</t>
+    <t>1.1809515275934706</t>
+  </si>
+  <si>
+    <t>1.2922942753064603</t>
+  </si>
+  <si>
+    <t>0.13550423546466028</t>
   </si>
   <si>
     <t>E1(exo)</t>
@@ -1564,13 +1564,13 @@
     <t>DSSYKIVIOFKYAU-OMNKOJBGSA-N</t>
   </si>
   <si>
-    <t>1.1047724102461856</t>
-  </si>
-  <si>
-    <t>0.6052060060924918</t>
-  </si>
-  <si>
-    <t>-0.541727620516643</t>
+    <t>1.1047724102461771</t>
+  </si>
+  <si>
+    <t>0.6052060060925326</t>
+  </si>
+  <si>
+    <t>-0.5417276205166022</t>
   </si>
   <si>
     <t>E1(endo)</t>
@@ -1585,13 +1585,13 @@
     <t>DSSYKIVIOFKYAU-MHPPCMCBSA-N</t>
   </si>
   <si>
-    <t>2.0782451913532367</t>
-  </si>
-  <si>
-    <t>1.796460600465498</t>
-  </si>
-  <si>
-    <t>-0.32764186197533407</t>
+    <t>2.078245191353209</t>
+  </si>
+  <si>
+    <t>1.7964606004654695</t>
+  </si>
+  <si>
+    <t>-0.3276418619753625</t>
   </si>
   <si>
     <t>E3(endo)</t>
@@ -1606,13 +1606,13 @@
     <t>LHXDLQBQYFFVNW-OMNKOJBGSA-N</t>
   </si>
   <si>
-    <t>1.1117898021731176</t>
-  </si>
-  <si>
-    <t>1.0219628350410384</t>
-  </si>
-  <si>
-    <t>-0.099504228002532</t>
+    <t>1.111789802173119</t>
+  </si>
+  <si>
+    <t>1.0219628350409913</t>
+  </si>
+  <si>
+    <t>-0.09950422800257908</t>
   </si>
   <si>
     <t>E3(exo)</t>
@@ -1627,13 +1627,13 @@
     <t>LHXDLQBQYFFVNW-MHPPCMCBSA-N</t>
   </si>
   <si>
-    <t>2.5790403680867415</t>
-  </si>
-  <si>
-    <t>2.1093842401658236</t>
-  </si>
-  <si>
-    <t>-0.5684930651185303</t>
+    <t>2.5790403680867167</t>
+  </si>
+  <si>
+    <t>2.1093842401657685</t>
+  </si>
+  <si>
+    <t>-0.5684930651185853</t>
   </si>
   <si>
     <t>A24</t>
@@ -1648,13 +1648,13 @@
     <t>UKQCJCWLKWRFFI-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>2.6074437073833923</t>
-  </si>
-  <si>
-    <t>2.083833198861619</t>
-  </si>
-  <si>
-    <t>-0.7462788549940447</t>
+    <t>2.607443707383389</t>
+  </si>
+  <si>
+    <t>2.0838331988616248</t>
+  </si>
+  <si>
+    <t>-0.7462788549940389</t>
   </si>
   <si>
     <t>a1</t>
@@ -1669,7 +1669,7 @@
     <t>XMRPGKVKISIQBV-KEOHVNNOSA-N</t>
   </si>
   <si>
-    <t>-0.3064355262966192</t>
+    <t>-0.30643552629662096</t>
   </si>
   <si>
     <t>a2</t>
@@ -1684,7 +1684,7 @@
     <t>XMRPGKVKISIQBV-RCNOZMPMSA-N</t>
   </si>
   <si>
-    <t>-0.9084958453951169</t>
+    <t>-0.9084958453950556</t>
   </si>
   <si>
     <t>a3</t>
@@ -1699,7 +1699,7 @@
     <t>XMRPGKVKISIQBV-XAHUAHKPSA-N</t>
   </si>
   <si>
-    <t>1.7631080218045612</t>
+    <t>1.763108021804649</t>
   </si>
   <si>
     <t>a4</t>
@@ -1714,7 +1714,7 @@
     <t>XMRPGKVKISIQBV-WGDJUOIDSA-N</t>
   </si>
   <si>
-    <t>1.2762853486055339</t>
+    <t>1.2762853486055876</t>
   </si>
   <si>
     <t>a13</t>
@@ -1729,7 +1729,7 @@
     <t>AURFZBICLPNKBZ-LNUOHZHLSA-N</t>
   </si>
   <si>
-    <t>0.9684530569570269</t>
+    <t>0.9684530569571379</t>
   </si>
   <si>
     <t>a14</t>
@@ -1744,7 +1744,7 @@
     <t>AURFZBICLPNKBZ-BKZNRXDMSA-N</t>
   </si>
   <si>
-    <t>0.4578603865505064</t>
+    <t>0.4578603865505091</t>
   </si>
   <si>
     <t>a23</t>
@@ -1759,7 +1759,7 @@
     <t>AURFZBICLPNKBZ-KRXPQHRASA-N</t>
   </si>
   <si>
-    <t>1.0441321712399851</t>
+    <t>1.044132171240085</t>
   </si>
   <si>
     <t>a24</t>
@@ -1774,7 +1774,7 @@
     <t>AURFZBICLPNKBZ-VYMTVNFKSA-N</t>
   </si>
   <si>
-    <t>0.5275757559203056</t>
+    <t>0.5275757559203065</t>
   </si>
   <si>
     <t>a41</t>
@@ -1789,7 +1789,7 @@
     <t>DYVGYXXLXQESJE-ASZUNUTGSA-N</t>
   </si>
   <si>
-    <t>-1.2295036923954488</t>
+    <t>-1.2295036923954337</t>
   </si>
   <si>
     <t>a42</t>
@@ -1804,7 +1804,7 @@
     <t>DYVGYXXLXQESJE-VMCDEYIWSA-N</t>
   </si>
   <si>
-    <t>-1.7785861492434236</t>
+    <t>-1.7785861492434059</t>
   </si>
   <si>
     <t>a31</t>
@@ -1819,7 +1819,7 @@
     <t>DYVGYXXLXQESJE-IEPKGJLISA-N</t>
   </si>
   <si>
-    <t>-1.024124529239514</t>
+    <t>-1.0241245292395122</t>
   </si>
   <si>
     <t>a32</t>
@@ -1834,7 +1834,7 @@
     <t>DYVGYXXLXQESJE-FXIFETPDSA-N</t>
   </si>
   <si>
-    <t>-2.012033207758124</t>
+    <t>-2.0120332077581393</t>
   </si>
   <si>
     <t>b1</t>
@@ -1843,13 +1843,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (diketone to trans-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]2C(=O)C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>FKXQMWVVHBPGAM-WAEWIHEKSA-N</t>
-  </si>
-  <si>
-    <t>-2.491489496282112</t>
+    <t>O=[13C]1C[C@@H]2C(=O)C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>FKXQMWVVHBPGAM-YDEWJKEYSA-N</t>
+  </si>
+  <si>
+    <t>-2.1460721451405202</t>
   </si>
   <si>
     <t>b2</t>
@@ -1858,13 +1858,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (diketone to cis-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]2C(=O)C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>FKXQMWVVHBPGAM-MJZUOOAJSA-N</t>
-  </si>
-  <si>
-    <t>2.142498930082385</t>
+    <t>O=[13C]1C[C@H]2C(=O)C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>FKXQMWVVHBPGAM-SBUADZPKSA-N</t>
+  </si>
+  <si>
+    <t>-0.1874003719426227</t>
   </si>
   <si>
     <t>b3</t>
@@ -1873,13 +1873,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (diketone to trans-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CCC(=O)C[C@H]12</t>
-  </si>
-  <si>
-    <t>FKXQMWVVHBPGAM-JJBCIBBMSA-N</t>
-  </si>
-  <si>
-    <t>-0.16699690694396807</t>
+    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CCC(=O)C[C@H]12</t>
+  </si>
+  <si>
+    <t>FKXQMWVVHBPGAM-ZZVOHZKGSA-N</t>
+  </si>
+  <si>
+    <t>0.15528847871954632</t>
   </si>
   <si>
     <t>b4</t>
@@ -1888,13 +1888,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (diketone to cis-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CCC(=O)C[C@@H]12</t>
-  </si>
-  <si>
-    <t>FKXQMWVVHBPGAM-SKWZSXOISA-N</t>
-  </si>
-  <si>
-    <t>2.9229964943516675</t>
+    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CCC(=O)C[C@@H]12</t>
+  </si>
+  <si>
+    <t>FKXQMWVVHBPGAM-SSWDLXJHSA-N</t>
+  </si>
+  <si>
+    <t>-0.12355607588084183</t>
   </si>
   <si>
     <t>b13</t>
@@ -1903,13 +1903,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (trans-3ol to trans-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CC[C@H](O)C[C@H]12</t>
-  </si>
-  <si>
-    <t>GQPXPLNWQRGXOX-JNQQBPBDSA-N</t>
-  </si>
-  <si>
-    <t>-0.9236152745068447</t>
+    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CC[C@H](O)C[C@H]12</t>
+  </si>
+  <si>
+    <t>GQPXPLNWQRGXOX-CNBRFADUSA-N</t>
+  </si>
+  <si>
+    <t>0.34504597641435186</t>
   </si>
   <si>
     <t>b14</t>
@@ -1918,13 +1918,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (trans-3ol to cis-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CC[C@@H](O)C[C@@H]12</t>
-  </si>
-  <si>
-    <t>GQPXPLNWQRGXOX-IKLYCGCASA-N</t>
-  </si>
-  <si>
-    <t>1.6103691012204138</t>
+    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CC[C@@H](O)C[C@@H]12</t>
+  </si>
+  <si>
+    <t>GQPXPLNWQRGXOX-RQSFXVAFSA-N</t>
+  </si>
+  <si>
+    <t>2.3859560008493528</t>
   </si>
   <si>
     <t>b23</t>
@@ -1933,13 +1933,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (cis-3ol to trans-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CC[C@@H](O)C[C@H]12</t>
-  </si>
-  <si>
-    <t>GQPXPLNWQRGXOX-GYSKMSRGSA-N</t>
-  </si>
-  <si>
-    <t>0.27226473712926325</t>
+    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CC[C@@H](O)C[C@H]12</t>
+  </si>
+  <si>
+    <t>GQPXPLNWQRGXOX-BJCYANKKSA-N</t>
+  </si>
+  <si>
+    <t>0.7033245403023054</t>
   </si>
   <si>
     <t>b24</t>
@@ -1948,13 +1948,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (cis-3ol to cis-6ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CC[C@H](O)C[C@@H]12</t>
-  </si>
-  <si>
-    <t>GQPXPLNWQRGXOX-YIUXRUQNSA-N</t>
-  </si>
-  <si>
-    <t>0.7245127721565119</t>
+    <t>O=[13C]1C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CC[C@H](O)C[C@@H]12</t>
+  </si>
+  <si>
+    <t>GQPXPLNWQRGXOX-DVSYPHBRSA-N</t>
+  </si>
+  <si>
+    <t>-0.4176821596561817</t>
   </si>
   <si>
     <t>b31</t>
@@ -1963,13 +1963,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (trans-6ol to trans-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]2[C@H](O)C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>MTFFDDCFMIWJPC-OIFMBHAESA-N</t>
-  </si>
-  <si>
-    <t>-0.9414259957491815</t>
+    <t>O=[13C]1C[C@@H]2[C@H](O)C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>MTFFDDCFMIWJPC-NOGVDBCPSA-N</t>
+  </si>
+  <si>
+    <t>-0.8555376468396663</t>
   </si>
   <si>
     <t>b32</t>
@@ -1978,13 +1978,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (trans-6ol to cis-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]2[C@@H](O)C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>MTFFDDCFMIWJPC-QCYVYVTOSA-N</t>
-  </si>
-  <si>
-    <t>2.2992716460177642</t>
+    <t>O=[13C]1C[C@H]2[C@@H](O)C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>MTFFDDCFMIWJPC-XNVXNBRISA-N</t>
+  </si>
+  <si>
+    <t>-0.9952599336191268</t>
   </si>
   <si>
     <t>b41</t>
@@ -1993,13 +1993,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (cis-6ol to trans-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@@H]2[C@@H](O)C[C@H]3[C@@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@@H]3[C@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>MTFFDDCFMIWJPC-VEBGLHEVSA-N</t>
-  </si>
-  <si>
-    <t>-0.25889326121386347</t>
+    <t>O=[13C]1C[C@@H]2[C@@H](O)C[C@@H]3[C@H]4CC[C@@H]([C@@H](C)C=C)[C@]4(C)CC[C@H]3[C@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>MTFFDDCFMIWJPC-XIEGWDQJSA-N</t>
+  </si>
+  <si>
+    <t>-1.2587178397111236</t>
   </si>
   <si>
     <t>b42</t>
@@ -2008,13 +2008,13 @@
     <t>24-nor-5β-chol-22-ene-3,6-dione (cis-6ol to cis-3ol)</t>
   </si>
   <si>
-    <t>O=[13C]1C[C@H]2[C@H](O)C[C@@H]3[C@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@H]3[C@@]2(C)CC1</t>
-  </si>
-  <si>
-    <t>MTFFDDCFMIWJPC-DDOLKKTRSA-N</t>
-  </si>
-  <si>
-    <t>-0.23156534992347133</t>
+    <t>O=[13C]1C[C@H]2[C@H](O)C[C@H]3[C@@H]4CC[C@H]([C@H](C)C=C)[C@@]4(C)CC[C@@H]3[C@@]2(C)CC1</t>
+  </si>
+  <si>
+    <t>MTFFDDCFMIWJPC-CMOIDRFCSA-N</t>
+  </si>
+  <si>
+    <t>-1.8194383698527163</t>
   </si>
   <si>
     <t>c1</t>
@@ -2029,7 +2029,7 @@
     <t>JZYUFCHBGFELAZ-DVPIJTCCSA-N</t>
   </si>
   <si>
-    <t>0.7120596457033619</t>
+    <t>0.7120596457029347</t>
   </si>
   <si>
     <t>c2</t>
@@ -2044,7 +2044,7 @@
     <t>JZYUFCHBGFELAZ-LRLPPDEGSA-N</t>
   </si>
   <si>
-    <t>-3.835932244992196</t>
+    <t>-3.8359322449918114</t>
   </si>
   <si>
     <t>c3</t>
@@ -2059,7 +2059,7 @@
     <t>JZYUFCHBGFELAZ-BROKRERSSA-N</t>
   </si>
   <si>
-    <t>3.6464344585160866</t>
+    <t>3.646434458516203</t>
   </si>
   <si>
     <t>c4</t>
@@ -2074,7 +2074,7 @@
     <t>JZYUFCHBGFELAZ-OYPDEIEDSA-N</t>
   </si>
   <si>
-    <t>1.7801353179240715</t>
+    <t>1.7801353179238841</t>
   </si>
   <si>
     <t>c13</t>
@@ -2089,7 +2089,7 @@
     <t>CPGUTDZBKMREHK-QFFGSERESA-N</t>
   </si>
   <si>
-    <t>4.361216758584887</t>
+    <t>4.361216758584919</t>
   </si>
   <si>
     <t>c14</t>
@@ -2104,7 +2104,7 @@
     <t>CPGUTDZBKMREHK-PSJJKCFBSA-N</t>
   </si>
   <si>
-    <t>2.2918002774905837</t>
+    <t>2.2918002774905006</t>
   </si>
   <si>
     <t>c23</t>
@@ -2119,7 +2119,7 @@
     <t>CPGUTDZBKMREHK-VNSKILTCSA-N</t>
   </si>
   <si>
-    <t>3.227308059264936</t>
+    <t>3.2273080592649834</t>
   </si>
   <si>
     <t>c24</t>
@@ -2134,7 +2134,7 @@
     <t>CPGUTDZBKMREHK-WPLBZINNSA-N</t>
   </si>
   <si>
-    <t>1.2625329158040932</t>
+    <t>1.2625329158039675</t>
   </si>
   <si>
     <t>c31</t>
@@ -2149,7 +2149,7 @@
     <t>DLDDAANYSAREPT-WWFPUDJXSA-N</t>
   </si>
   <si>
-    <t>2.3696974530710735</t>
+    <t>2.369697453071287</t>
   </si>
   <si>
     <t>c32</t>
@@ -2164,7 +2164,7 @@
     <t>DLDDAANYSAREPT-RZXYCCSUSA-N</t>
   </si>
   <si>
-    <t>-0.314114338151251</t>
+    <t>-0.31411433815113643</t>
   </si>
   <si>
     <t>c41</t>
@@ -2179,7 +2179,7 @@
     <t>DLDDAANYSAREPT-ZAXYEOTCSA-N</t>
   </si>
   <si>
-    <t>3.761712718818454</t>
+    <t>3.7617127188181945</t>
   </si>
   <si>
     <t>c42</t>
@@ -2194,7 +2194,7 @@
     <t>DLDDAANYSAREPT-RWZHDOEGSA-N</t>
   </si>
   <si>
-    <t>-1.6262083987697658</t>
+    <t>-1.626208398769541</t>
   </si>
   <si>
     <t>d1</t>
@@ -2209,7 +2209,7 @@
     <t>PLSRWRBYAQQGNN-YMICIMMMSA-N</t>
   </si>
   <si>
-    <t>-0.7419364204337437</t>
+    <t>-0.7419364204336594</t>
   </si>
   <si>
     <t>d2</t>
@@ -2224,7 +2224,7 @@
     <t>PLSRWRBYAQQGNN-PGRCEAHZSA-N</t>
   </si>
   <si>
-    <t>2.956233629034572</t>
+    <t>2.9562336290346316</t>
   </si>
   <si>
     <t>d3</t>
@@ -2239,7 +2239,7 @@
     <t>PLSRWRBYAQQGNN-UWMVLEJGSA-N</t>
   </si>
   <si>
-    <t>2.679315708370792</t>
+    <t>2.679315708370855</t>
   </si>
   <si>
     <t>d4</t>
@@ -2254,7 +2254,7 @@
     <t>PLSRWRBYAQQGNN-DDOBXCKSSA-N</t>
   </si>
   <si>
-    <t>5.24667696777456</t>
+    <t>5.246676967774671</t>
   </si>
   <si>
     <t>d13</t>
@@ -2269,7 +2269,7 @@
     <t>PVVDMQFIFUBDPK-DBCKSZCESA-N</t>
   </si>
   <si>
-    <t>2.8681768771719103</t>
+    <t>2.8681768771719263</t>
   </si>
   <si>
     <t>d14</t>
@@ -2284,7 +2284,7 @@
     <t>PVVDMQFIFUBDPK-JIFCSIQBSA-N</t>
   </si>
   <si>
-    <t>5.855166981811612</t>
+    <t>5.855166981811712</t>
   </si>
   <si>
     <t>d23</t>
@@ -2299,7 +2299,7 @@
     <t>PVVDMQFIFUBDPK-NDZOIIPPSA-N</t>
   </si>
   <si>
-    <t>2.914011899980386</t>
+    <t>2.914011899980426</t>
   </si>
   <si>
     <t>d24</t>
@@ -2314,7 +2314,7 @@
     <t>PVVDMQFIFUBDPK-GTENJMHGSA-N</t>
   </si>
   <si>
-    <t>5.19494999423054</t>
+    <t>5.194949994230648</t>
   </si>
   <si>
     <t>d31</t>
@@ -2329,7 +2329,7 @@
     <t>NRDYHKKVKIBAKC-MNOSHWMVSA-N</t>
   </si>
   <si>
-    <t>0.039140328793410006</t>
+    <t>0.03914032879347662</t>
   </si>
   <si>
     <t>d32</t>
@@ -2344,7 +2344,7 @@
     <t>NRDYHKKVKIBAKC-OWQDIHQOSA-N</t>
   </si>
   <si>
-    <t>3.2539318233321275</t>
+    <t>3.2539318233321834</t>
   </si>
   <si>
     <t>d41</t>
@@ -2359,7 +2359,7 @@
     <t>NRDYHKKVKIBAKC-JOSUAJGWSA-N</t>
   </si>
   <si>
-    <t>0.011711880454855716</t>
+    <t>0.011711880454944534</t>
   </si>
   <si>
     <t>d42</t>
@@ -2374,7 +2374,7 @@
     <t>NRDYHKKVKIBAKC-YSWLJETKSA-N</t>
   </si>
   <si>
-    <t>2.0862052515964042</t>
+    <t>2.086205251596476</t>
   </si>
   <si>
     <t>e1</t>
@@ -2389,7 +2389,7 @@
     <t>UVBDRYIUPXGITC-LBAGWYSSSA-N</t>
   </si>
   <si>
-    <t>1.4102415849655907</t>
+    <t>1.4102415849640866</t>
   </si>
   <si>
     <t>e2</t>
@@ -2404,7 +2404,7 @@
     <t>UVBDRYIUPXGITC-CGTNMINPSA-N</t>
   </si>
   <si>
-    <t>-5.462213473683881</t>
+    <t>-5.462213473683008</t>
   </si>
   <si>
     <t>e3</t>
@@ -2419,7 +2419,7 @@
     <t>UVBDRYIUPXGITC-YEOVCMATSA-N</t>
   </si>
   <si>
-    <t>0.3251901636366217</t>
+    <t>0.32519016363579567</t>
   </si>
   <si>
     <t>e4</t>
@@ -2434,7 +2434,7 @@
     <t>UVBDRYIUPXGITC-DOYIJFFUSA-N</t>
   </si>
   <si>
-    <t>-1.7363923987679035</t>
+    <t>-1.7363923987672472</t>
   </si>
   <si>
     <t>e13</t>
@@ -2449,7 +2449,7 @@
     <t>IVOMJTYTUMAEPU-BNYPWJEISA-N</t>
   </si>
   <si>
-    <t>-0.3465809097397825</t>
+    <t>-0.3465809097400596</t>
   </si>
   <si>
     <t>e14</t>
@@ -2464,7 +2464,7 @@
     <t>IVOMJTYTUMAEPU-IFVVCBRGSA-N</t>
   </si>
   <si>
-    <t>7.034023144802653</t>
+    <t>7.034023144803187</t>
   </si>
   <si>
     <t>e23</t>
@@ -2479,7 +2479,7 @@
     <t>IVOMJTYTUMAEPU-NHUKILISSA-N</t>
   </si>
   <si>
-    <t>2.3862610402852225</t>
+    <t>2.386261040284874</t>
   </si>
   <si>
     <t>e24</t>
@@ -2494,7 +2494,7 @@
     <t>IVOMJTYTUMAEPU-NTZOYJIVSA-N</t>
   </si>
   <si>
-    <t>5.2566408580845625</t>
+    <t>5.25664085808489</t>
   </si>
   <si>
     <t>e31</t>
@@ -2509,7 +2509,7 @@
     <t>CIHUIHZNFZBJLT-YMEMZECQSA-N</t>
   </si>
   <si>
-    <t>0.9423274773795205</t>
+    <t>0.942327477379477</t>
   </si>
   <si>
     <t>e32</t>
@@ -2524,7 +2524,7 @@
     <t>CIHUIHZNFZBJLT-NIHYJFBUSA-N</t>
   </si>
   <si>
-    <t>1.82103572994304</t>
+    <t>1.821035729943143</t>
   </si>
   <si>
     <t>e41</t>
@@ -2539,7 +2539,7 @@
     <t>CIHUIHZNFZBJLT-FLCNWGKISA-N</t>
   </si>
   <si>
-    <t>2.6969585619409657</t>
+    <t>2.696958561940702</t>
   </si>
   <si>
     <t>e42</t>
@@ -2554,7 +2554,7 @@
     <t>CIHUIHZNFZBJLT-SVCHTCNZSA-N</t>
   </si>
   <si>
-    <t>1.7015144551444852</t>
+    <t>1.701514455144649</t>
   </si>
   <si>
     <t>f1</t>
@@ -2569,7 +2569,7 @@
     <t>OLTFXJBPGNUYCS-SXWDLQOWSA-N</t>
   </si>
   <si>
-    <t>-0.6604462029489007</t>
+    <t>-0.6604462029491387</t>
   </si>
   <si>
     <t>f2</t>
@@ -2584,7 +2584,7 @@
     <t>OLTFXJBPGNUYCS-HMOKLJILSA-N</t>
   </si>
   <si>
-    <t>1.2443564098742579</t>
+    <t>1.2443564098744653</t>
   </si>
   <si>
     <t>f3</t>
@@ -2599,7 +2599,7 @@
     <t>OLTFXJBPGNUYCS-UQVPQUPTSA-N</t>
   </si>
   <si>
-    <t>0.62986593818838</t>
+    <t>0.6298659381882308</t>
   </si>
   <si>
     <t>f4</t>
@@ -2614,7 +2614,7 @@
     <t>OLTFXJBPGNUYCS-TUZJZFOZSA-N</t>
   </si>
   <si>
-    <t>0.2546003438494484</t>
+    <t>0.25460034384958163</t>
   </si>
   <si>
     <t>f31</t>
@@ -2629,7 +2629,7 @@
     <t>YNUSLOYDHGAYPB-XFQCTZMHSA-N</t>
   </si>
   <si>
-    <t>-0.9296980737878968</t>
+    <t>-0.9296980737879492</t>
   </si>
   <si>
     <t>f41</t>
@@ -2644,7 +2644,7 @@
     <t>YNUSLOYDHGAYPB-DUGYZFACSA-N</t>
   </si>
   <si>
-    <t>0.06619724622552958</t>
+    <t>0.06619724622554468</t>
   </si>
   <si>
     <t>f42</t>
@@ -2659,7 +2659,7 @@
     <t>YNUSLOYDHGAYPB-PVGPVLRXSA-N</t>
   </si>
   <si>
-    <t>2.1956939369218227</t>
+    <t>2.1956939369219133</t>
   </si>
   <si>
     <t>f32</t>
@@ -2674,7 +2674,7 @@
     <t>YNUSLOYDHGAYPB-KGJWWKPOSA-N</t>
   </si>
   <si>
-    <t>2.6423637108151947</t>
+    <t>2.6423637108153843</t>
   </si>
   <si>
     <t>f13</t>
@@ -2689,7 +2689,7 @@
     <t>YRPUMHYLNYRQGZ-RGVIPMAXSA-N</t>
   </si>
   <si>
-    <t>0.3954519766512439</t>
+    <t>0.3954519766512421</t>
   </si>
   <si>
     <t>f23</t>
@@ -2704,7 +2704,7 @@
     <t>YRPUMHYLNYRQGZ-SMKLAQEQSA-N</t>
   </si>
   <si>
-    <t>1.4206484267100326</t>
+    <t>1.420648426710022</t>
   </si>
   <si>
     <t>f24</t>
@@ -2719,7 +2719,7 @@
     <t>YRPUMHYLNYRQGZ-HEENYJBUSA-N</t>
   </si>
   <si>
-    <t>3.8264315374126934</t>
+    <t>3.8264315374127813</t>
   </si>
   <si>
     <t>f14</t>
@@ -2734,7 +2734,7 @@
     <t>YRPUMHYLNYRQGZ-ZUBQCWPDSA-N</t>
   </si>
   <si>
-    <t>1.4188328986787506</t>
+    <t>1.418832898678993</t>
   </si>
 </sst>
 </file>
@@ -8765,16 +8765,16 @@
         <v>-2.60113029402424</v>
       </c>
       <c r="F2">
-        <v>-4.171965980163237</v>
+        <v>-4.171965980163747</v>
       </c>
       <c r="G2">
-        <v>-1.544734425234906</v>
+        <v>-1.544734425235027</v>
       </c>
       <c r="H2">
-        <v>-1.821772030281592</v>
+        <v>-1.821772030281682</v>
       </c>
       <c r="I2">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -8809,16 +8809,16 @@
         <v>-2.326661474907522</v>
       </c>
       <c r="F3">
-        <v>-4.942399702758855</v>
+        <v>-4.94239970275946</v>
       </c>
       <c r="G3">
-        <v>-2.462781176188992</v>
+        <v>-2.462781176189006</v>
       </c>
       <c r="H3">
-        <v>0.09823561337190395</v>
+        <v>0.09823561337184661</v>
       </c>
       <c r="I3">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
@@ -8853,16 +8853,16 @@
         <v>-2.101963024860244</v>
       </c>
       <c r="F4">
-        <v>-4.957728099565425</v>
+        <v>-4.957728099565843</v>
       </c>
       <c r="G4">
-        <v>-0.9573759994649795</v>
+        <v>-0.9573759994651501</v>
       </c>
       <c r="H4">
-        <v>-0.9142573807833677</v>
+        <v>-0.9142573807834713</v>
       </c>
       <c r="I4">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J4" t="s">
         <v>34</v>
@@ -8897,16 +8897,16 @@
         <v>-2.101787997359787</v>
       </c>
       <c r="F5">
-        <v>-3.64159952146959</v>
+        <v>-3.641599521470071</v>
       </c>
       <c r="G5">
-        <v>-3.903847146570891</v>
+        <v>-3.903847146571017</v>
       </c>
       <c r="H5">
-        <v>0.5168749555197325</v>
+        <v>0.5168749555196434</v>
       </c>
       <c r="I5">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J5" t="s">
         <v>41</v>
@@ -8941,16 +8941,16 @@
         <v>-2.284136805132168</v>
       </c>
       <c r="F6">
-        <v>-5.238192524244182</v>
+        <v>-5.23819252424452</v>
       </c>
       <c r="G6">
-        <v>-0.1015471893423134</v>
+        <v>-0.1015471893425963</v>
       </c>
       <c r="H6">
-        <v>-1.792970393514266</v>
+        <v>-1.792970393514339</v>
       </c>
       <c r="I6">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J6" t="s">
         <v>48</v>
@@ -8985,16 +8985,16 @@
         <v>-1.580941232231622</v>
       </c>
       <c r="F7">
-        <v>-4.355845184229797</v>
+        <v>-4.355845184230478</v>
       </c>
       <c r="G7">
-        <v>-0.5768360805905339</v>
+        <v>-0.5768360805905273</v>
       </c>
       <c r="H7">
-        <v>-1.455979288497041</v>
+        <v>-1.455979288497037</v>
       </c>
       <c r="I7">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J7" t="s">
         <v>55</v>
@@ -9029,16 +9029,16 @@
         <v>-2.018447407001851</v>
       </c>
       <c r="F8">
-        <v>-4.160065492935935</v>
+        <v>-4.160065492936553</v>
       </c>
       <c r="G8">
-        <v>-2.235931112167703</v>
+        <v>-2.235931112167733</v>
       </c>
       <c r="H8">
-        <v>-0.7059412972362507</v>
+        <v>-0.7059412972362704</v>
       </c>
       <c r="I8">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J8" t="s">
         <v>62</v>
@@ -9073,16 +9073,16 @@
         <v>-2.103421857962737</v>
       </c>
       <c r="F9">
-        <v>-5.315513040037192</v>
+        <v>-5.315513040037564</v>
       </c>
       <c r="G9">
-        <v>-0.4803893189752646</v>
+        <v>-0.4803893189755017</v>
       </c>
       <c r="H9">
-        <v>-1.274250985351067</v>
+        <v>-1.274250985351145</v>
       </c>
       <c r="I9">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J9" t="s">
         <v>69</v>
@@ -9117,16 +9117,16 @@
         <v>-1.502819090913842</v>
       </c>
       <c r="F10">
-        <v>-4.387977921024224</v>
+        <v>-4.387977921024843</v>
       </c>
       <c r="G10">
-        <v>-0.9353958035833712</v>
+        <v>-0.9353958035834085</v>
       </c>
       <c r="H10">
-        <v>-1.100769702943957</v>
+        <v>-1.100769702943977</v>
       </c>
       <c r="I10">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J10" t="s">
         <v>76</v>
@@ -9161,16 +9161,16 @@
         <v>-1.806620265267198</v>
       </c>
       <c r="F11">
-        <v>-4.859597478934594</v>
+        <v>-4.859597478935163</v>
       </c>
       <c r="G11">
-        <v>-0.8240220602192498</v>
+        <v>-0.8240220602193387</v>
       </c>
       <c r="H11">
-        <v>-1.112224808893304</v>
+        <v>-1.112224808893322</v>
       </c>
       <c r="I11">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J11" t="s">
         <v>83</v>
@@ -9205,16 +9205,16 @@
         <v>-1.795055348560182</v>
       </c>
       <c r="F12">
-        <v>-4.133136011615305</v>
+        <v>-4.133136011615929</v>
       </c>
       <c r="G12">
-        <v>-1.728391967902186</v>
+        <v>-1.728391967902217</v>
       </c>
       <c r="H12">
-        <v>-0.8039346447567354</v>
+        <v>-0.8039346447568101</v>
       </c>
       <c r="I12">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J12" t="s">
         <v>90</v>
@@ -9249,16 +9249,16 @@
         <v>-1.725565946217091</v>
       </c>
       <c r="F13">
-        <v>-4.562924128830543</v>
+        <v>-4.562924128830978</v>
       </c>
       <c r="G13">
-        <v>-1.882244896606868</v>
+        <v>-1.882244896607156</v>
       </c>
       <c r="H13">
-        <v>-0.2611933987888153</v>
+        <v>-0.2611933987887547</v>
       </c>
       <c r="I13">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J13" t="s">
         <v>97</v>
@@ -9293,16 +9293,16 @@
         <v>-2.531608279164891</v>
       </c>
       <c r="F14">
-        <v>-5.453834296078653</v>
+        <v>-5.453834296078998</v>
       </c>
       <c r="G14">
-        <v>-0.6582874740453097</v>
+        <v>-0.6582874740455615</v>
       </c>
       <c r="H14">
-        <v>-1.326179506770528</v>
+        <v>-1.326179506770635</v>
       </c>
       <c r="I14">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J14" t="s">
         <v>104</v>
@@ -9337,16 +9337,16 @@
         <v>-1.728599854316544</v>
       </c>
       <c r="F15">
-        <v>-4.377298112760282</v>
+        <v>-4.377298112760972</v>
       </c>
       <c r="G15">
-        <v>-1.261200945342662</v>
+        <v>-1.261200945342668</v>
       </c>
       <c r="H15">
-        <v>-1.148823773719909</v>
+        <v>-1.148823773719896</v>
       </c>
       <c r="I15">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J15" t="s">
         <v>111</v>
@@ -9381,16 +9381,16 @@
         <v>-2.083553479163855</v>
       </c>
       <c r="F16">
-        <v>-4.898271644796486</v>
+        <v>-4.898271644797012</v>
       </c>
       <c r="G16">
-        <v>-0.6667213216076142</v>
+        <v>-0.6667213216077426</v>
       </c>
       <c r="H16">
-        <v>-1.513104314034984</v>
+        <v>-1.513104314035016</v>
       </c>
       <c r="I16">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J16" t="s">
         <v>118</v>
@@ -9425,16 +9425,16 @@
         <v>-1.749319747694561</v>
       </c>
       <c r="F17">
-        <v>-4.823241065905725</v>
+        <v>-4.823241065906229</v>
       </c>
       <c r="G17">
-        <v>-0.3147048910138657</v>
+        <v>-0.3147048910139256</v>
       </c>
       <c r="H17">
-        <v>-1.529597310079336</v>
+        <v>-1.529597310079461</v>
       </c>
       <c r="I17">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J17" t="s">
         <v>125</v>
@@ -9469,16 +9469,16 @@
         <v>-1.969126312089138</v>
       </c>
       <c r="F18">
-        <v>-3.273834640851038</v>
+        <v>-3.273834640851255</v>
       </c>
       <c r="G18">
-        <v>-3.246152879951121</v>
+        <v>-3.246152879951238</v>
       </c>
       <c r="H18">
-        <v>-0.4464653049705844</v>
+        <v>-0.4464653049709304</v>
       </c>
       <c r="I18">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J18" t="s">
         <v>132</v>
@@ -9513,16 +9513,16 @@
         <v>-0.9119717054118576</v>
       </c>
       <c r="F19">
-        <v>-2.878752143572801</v>
+        <v>-2.878752143573382</v>
       </c>
       <c r="G19">
-        <v>-1.990425753733164</v>
+        <v>-1.990425753733417</v>
       </c>
       <c r="H19">
-        <v>-1.03993256258791</v>
+        <v>-1.039932562587745</v>
       </c>
       <c r="I19">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J19" t="s">
         <v>139</v>
@@ -9557,16 +9557,16 @@
         <v>-1.584197909427703</v>
       </c>
       <c r="F20">
-        <v>-4.276327540500196</v>
+        <v>-4.276327540500755</v>
       </c>
       <c r="G20">
-        <v>-1.314030289329271</v>
+        <v>-1.314030289329315</v>
       </c>
       <c r="H20">
-        <v>-0.6779960144548162</v>
+        <v>-0.6779960144548985</v>
       </c>
       <c r="I20">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J20" t="s">
         <v>146</v>
@@ -9601,16 +9601,16 @@
         <v>-1.470473783294095</v>
       </c>
       <c r="F21">
-        <v>-4.813738720069377</v>
+        <v>-4.813738720069808</v>
       </c>
       <c r="G21">
-        <v>0.2639112810111124</v>
+        <v>0.2639112810108659</v>
       </c>
       <c r="H21">
-        <v>-1.804826295740529</v>
+        <v>-1.804826295740542</v>
       </c>
       <c r="I21">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J21" t="s">
         <v>153</v>
@@ -9645,16 +9645,16 @@
         <v>-1.46340509593633</v>
       </c>
       <c r="F22">
-        <v>-4.224902671037195</v>
+        <v>-4.2249026710378</v>
       </c>
       <c r="G22">
-        <v>-1.55500405776491</v>
+        <v>-1.555004057764942</v>
       </c>
       <c r="H22">
-        <v>-0.5629177506308736</v>
+        <v>-0.5629177506309295</v>
       </c>
       <c r="I22">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J22" t="s">
         <v>160</v>
@@ -9689,16 +9689,16 @@
         <v>-1.184470892261653</v>
       </c>
       <c r="F23">
-        <v>-4.062709105887879</v>
+        <v>-4.062709105888409</v>
       </c>
       <c r="G23">
-        <v>-1.45773568460777</v>
+        <v>-1.45773568460784</v>
       </c>
       <c r="H23">
-        <v>-0.8268346199547907</v>
+        <v>-0.8268346199548608</v>
       </c>
       <c r="I23">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J23" t="s">
         <v>167</v>
@@ -9733,16 +9733,16 @@
         <v>-1.139750790027024</v>
       </c>
       <c r="F24">
-        <v>-4.4811259723649</v>
+        <v>-4.481125972365503</v>
       </c>
       <c r="G24">
-        <v>-1.161648970401584</v>
+        <v>-1.161648970401638</v>
       </c>
       <c r="H24">
-        <v>-0.5162587918572833</v>
+        <v>-0.5162587918573014</v>
       </c>
       <c r="I24">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J24" t="s">
         <v>174</v>
@@ -9777,16 +9777,16 @@
         <v>-0.8821075033688486</v>
       </c>
       <c r="F25">
-        <v>-3.885119112402465</v>
+        <v>-3.885119112403053</v>
       </c>
       <c r="G25">
-        <v>-0.7165024933940036</v>
+        <v>-0.716502493394084</v>
       </c>
       <c r="H25">
-        <v>-1.216386711358041</v>
+        <v>-1.216386711358042</v>
       </c>
       <c r="I25">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J25" t="s">
         <v>181</v>
@@ -9821,16 +9821,16 @@
         <v>-0.8741251315776558</v>
       </c>
       <c r="F26">
-        <v>-4.198573551511886</v>
+        <v>-4.198573551512439</v>
       </c>
       <c r="G26">
-        <v>-0.855645851294911</v>
+        <v>-0.8556458512950131</v>
       </c>
       <c r="H26">
-        <v>-0.7626201254621358</v>
+        <v>-0.7626201254621582</v>
       </c>
       <c r="I26">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J26" t="s">
         <v>188</v>
@@ -9865,16 +9865,16 @@
         <v>-0.8119907764955839</v>
       </c>
       <c r="F27">
-        <v>-4.294880937926267</v>
+        <v>-4.294880937926711</v>
       </c>
       <c r="G27">
-        <v>-1.357808226430777</v>
+        <v>-1.357808226430904</v>
       </c>
       <c r="H27">
-        <v>-0.1167428459320472</v>
+        <v>-0.1167428459321423</v>
       </c>
       <c r="I27">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J27" t="s">
         <v>195</v>
@@ -9909,16 +9909,16 @@
         <v>-0.7959106766567086</v>
       </c>
       <c r="F28">
-        <v>-4.333790751485449</v>
+        <v>-4.333790751486057</v>
       </c>
       <c r="G28">
-        <v>-0.6045547432464553</v>
+        <v>-0.6045547432464904</v>
       </c>
       <c r="H28">
-        <v>-1.015852162989259</v>
+        <v>-1.01585216298929</v>
       </c>
       <c r="I28">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J28" t="s">
         <v>202</v>
@@ -9953,16 +9953,16 @@
         <v>-1.093032799535838</v>
       </c>
       <c r="F29">
-        <v>-3.953148241420399</v>
+        <v>-3.953148241421187</v>
       </c>
       <c r="G29">
-        <v>-0.7868422912627255</v>
+        <v>-0.7868422912626283</v>
       </c>
       <c r="H29">
-        <v>-1.283098882411803</v>
+        <v>-1.283098882411811</v>
       </c>
       <c r="I29">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J29" t="s">
         <v>209</v>
@@ -9997,16 +9997,16 @@
         <v>-0.1836116224693557</v>
       </c>
       <c r="F30">
-        <v>-3.913232328616052</v>
+        <v>-3.913232328616238</v>
       </c>
       <c r="G30">
-        <v>0.1977077468658104</v>
+        <v>0.1977077468653614</v>
       </c>
       <c r="H30">
-        <v>-1.382354129074483</v>
+        <v>-1.382354129074524</v>
       </c>
       <c r="I30">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J30" t="s">
         <v>216</v>
@@ -10041,16 +10041,16 @@
         <v>-0.7904736039696392</v>
       </c>
       <c r="F31">
-        <v>-4.277420594057376</v>
+        <v>-4.277420594057913</v>
       </c>
       <c r="G31">
-        <v>-0.9742342792449672</v>
+        <v>-0.974234279245016</v>
       </c>
       <c r="H31">
-        <v>-0.7464768850318463</v>
+        <v>-0.7464768850319448</v>
       </c>
       <c r="I31">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J31" t="s">
         <v>223</v>
@@ -10085,16 +10085,16 @@
         <v>-0.7672692930524473</v>
       </c>
       <c r="F32">
-        <v>-4.597373523356957</v>
+        <v>-4.597373523357471</v>
       </c>
       <c r="G32">
-        <v>-0.6255251600348151</v>
+        <v>-0.625525160034837</v>
       </c>
       <c r="H32">
-        <v>-0.5075228248606833</v>
+        <v>-0.5075228248608117</v>
       </c>
       <c r="I32">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J32" t="s">
         <v>230</v>
@@ -10129,16 +10129,16 @@
         <v>-0.7451105814624829</v>
       </c>
       <c r="F33">
-        <v>-4.262585539963148</v>
+        <v>-4.262585539963684</v>
       </c>
       <c r="G33">
-        <v>-0.8581733470136856</v>
+        <v>-0.8581733470137221</v>
       </c>
       <c r="H33">
-        <v>-0.8472541118274561</v>
+        <v>-0.8472541118275561</v>
       </c>
       <c r="I33">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J33" t="s">
         <v>237</v>
@@ -10173,16 +10173,16 @@
         <v>-0.5707522973278076</v>
       </c>
       <c r="F34">
-        <v>-3.733370969570287</v>
+        <v>-3.733370969570874</v>
       </c>
       <c r="G34">
-        <v>-0.6263127202662542</v>
+        <v>-0.626312720266192</v>
       </c>
       <c r="H34">
-        <v>-1.062596433110487</v>
+        <v>-1.062596433110617</v>
       </c>
       <c r="I34">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J34" t="s">
         <v>244</v>
@@ -10217,16 +10217,16 @@
         <v>-0.8985045618297822</v>
       </c>
       <c r="F35">
-        <v>-3.511359407639772</v>
+        <v>-3.511359407640344</v>
       </c>
       <c r="G35">
-        <v>-1.348035204253273</v>
+        <v>-1.348035204253359</v>
       </c>
       <c r="H35">
-        <v>-0.9955988620332552</v>
+        <v>-0.9955988620332663</v>
       </c>
       <c r="I35">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J35" t="s">
         <v>251</v>
@@ -10261,16 +10261,16 @@
         <v>0.5061094003213791</v>
       </c>
       <c r="F36">
-        <v>-3.230451459377176</v>
+        <v>-3.230451459377459</v>
       </c>
       <c r="G36">
-        <v>-0.3184644272720205</v>
+        <v>-0.3184644272723727</v>
       </c>
       <c r="H36">
-        <v>-0.836521584681857</v>
+        <v>-0.8365215846818965</v>
       </c>
       <c r="I36">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J36" t="s">
         <v>258</v>
@@ -10305,16 +10305,16 @@
         <v>-0.5417615135950751</v>
       </c>
       <c r="F37">
-        <v>-4.212737993303706</v>
+        <v>-4.21273799330417</v>
       </c>
       <c r="G37">
-        <v>-0.6870012745299712</v>
+        <v>-0.6870012745301017</v>
       </c>
       <c r="H37">
-        <v>-0.7017181280872928</v>
+        <v>-0.7017181280873698</v>
       </c>
       <c r="I37">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J37" t="s">
         <v>265</v>
@@ -10349,16 +10349,16 @@
         <v>-0.5180692507674259</v>
       </c>
       <c r="F38">
-        <v>-4.021882319718185</v>
+        <v>-4.02188231971871</v>
       </c>
       <c r="G38">
-        <v>-0.5539680146502413</v>
+        <v>-0.5539680146502617</v>
       </c>
       <c r="H38">
-        <v>-0.7716710291092073</v>
+        <v>-0.7716710291093274</v>
       </c>
       <c r="I38">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J38" t="s">
         <v>272</v>
@@ -10393,16 +10393,16 @@
         <v>-0.4811015603624227</v>
       </c>
       <c r="F39">
-        <v>-4.16119539478863</v>
+        <v>-4.16119539478925</v>
       </c>
       <c r="G39">
-        <v>-0.4915022453376232</v>
+        <v>-0.4915022453376365</v>
       </c>
       <c r="H39">
-        <v>-0.644927950571632</v>
+        <v>-0.6449279505716629</v>
       </c>
       <c r="I39">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J39" t="s">
         <v>279</v>
@@ -10437,16 +10437,16 @@
         <v>-0.4772220477077166</v>
       </c>
       <c r="F40">
-        <v>-3.759029976689391</v>
+        <v>-3.759029976689986</v>
       </c>
       <c r="G40">
-        <v>-1.462414793454025</v>
+        <v>-1.462414793454055</v>
       </c>
       <c r="H40">
-        <v>-0.1017797307757417</v>
+        <v>-0.1017797307758048</v>
       </c>
       <c r="I40">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J40" t="s">
         <v>286</v>
@@ -10481,16 +10481,16 @@
         <v>-0.738058924470881</v>
       </c>
       <c r="F41">
-        <v>-5.057425373933009</v>
+        <v>-5.057425373933418</v>
       </c>
       <c r="G41">
-        <v>0.90880189914559</v>
+        <v>0.9088018991454314</v>
       </c>
       <c r="H41">
-        <v>-1.650675709932112</v>
+        <v>-1.650675709932212</v>
       </c>
       <c r="I41">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J41" t="s">
         <v>293</v>
@@ -10525,16 +10525,16 @@
         <v>-0.119038461443138</v>
       </c>
       <c r="F42">
-        <v>-3.742506539418349</v>
+        <v>-3.742506539418996</v>
       </c>
       <c r="G42">
-        <v>0.5268553649141992</v>
+        <v>0.5268553649141228</v>
       </c>
       <c r="H42">
-        <v>-1.888130595666881</v>
+        <v>-1.888130595666846</v>
       </c>
       <c r="I42">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J42" t="s">
         <v>300</v>
@@ -10569,16 +10569,16 @@
         <v>-0.2799376933401825</v>
       </c>
       <c r="F43">
-        <v>-4.287390712388146</v>
+        <v>-4.28739071238878</v>
       </c>
       <c r="G43">
-        <v>0.07992962419480953</v>
+        <v>0.0799296241947931</v>
       </c>
       <c r="H43">
-        <v>-0.8694443734634947</v>
+        <v>-0.8694443734635328</v>
       </c>
       <c r="I43">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J43" t="s">
         <v>307</v>
@@ -10613,16 +10613,16 @@
         <v>-0.2711277995120343</v>
       </c>
       <c r="F44">
-        <v>-3.42889169160205</v>
+        <v>-3.428891691602534</v>
       </c>
       <c r="G44">
-        <v>-0.5906201811322522</v>
+        <v>-0.5906201811324436</v>
       </c>
       <c r="H44">
-        <v>-1.155186886124308</v>
+        <v>-1.155186886124348</v>
       </c>
       <c r="I44">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J44" t="s">
         <v>314</v>
@@ -10657,16 +10657,16 @@
         <v>-0.2513599155992569</v>
       </c>
       <c r="F45">
-        <v>-4.271497314934284</v>
+        <v>-4.271497314934893</v>
       </c>
       <c r="G45">
-        <v>-0.8419510670607453</v>
+        <v>-0.8419510670607582</v>
       </c>
       <c r="H45">
-        <v>-0.224542883604772</v>
+        <v>-0.2245428836048357</v>
       </c>
       <c r="I45">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J45" t="s">
         <v>321</v>
@@ -10701,16 +10701,16 @@
         <v>-0.2254492664000439</v>
       </c>
       <c r="F46">
-        <v>-3.896173473917452</v>
+        <v>-3.896173473918024</v>
       </c>
       <c r="G46">
-        <v>-0.605507298986216</v>
+        <v>-0.6055072989862378</v>
       </c>
       <c r="H46">
-        <v>-0.7132280506692419</v>
+        <v>-0.7132280506693411</v>
       </c>
       <c r="I46">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J46" t="s">
         <v>328</v>
@@ -10745,16 +10745,16 @@
         <v>-0.2106493011682326</v>
       </c>
       <c r="F47">
-        <v>-4.196286140639907</v>
+        <v>-4.19628614064052</v>
       </c>
       <c r="G47">
-        <v>-0.524601490549526</v>
+        <v>-0.5246014905495362</v>
       </c>
       <c r="H47">
-        <v>-0.4179426476529403</v>
+        <v>-0.417942647652996</v>
       </c>
       <c r="I47">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J47" t="s">
         <v>335</v>
@@ -10789,16 +10789,16 @@
         <v>-0.2092560146496584</v>
       </c>
       <c r="F48">
-        <v>-4.106971914817158</v>
+        <v>-4.106971914817786</v>
       </c>
       <c r="G48">
-        <v>-0.2599568361988416</v>
+        <v>-0.2599568361988367</v>
       </c>
       <c r="H48">
-        <v>-0.9244602253126448</v>
+        <v>-0.9244602253127023</v>
       </c>
       <c r="I48">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J48" t="s">
         <v>342</v>
@@ -10833,16 +10833,16 @@
         <v>-0.1954892739093503</v>
       </c>
       <c r="F49">
-        <v>-4.158892454165708</v>
+        <v>-4.158892454166238</v>
       </c>
       <c r="G49">
-        <v>-0.7253641479127819</v>
+        <v>-0.7253641479129036</v>
       </c>
       <c r="H49">
-        <v>-0.3335120456310522</v>
+        <v>-0.3335120456310859</v>
       </c>
       <c r="I49">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J49" t="s">
         <v>349</v>
@@ -10877,16 +10877,16 @@
         <v>-0.1400583315037466</v>
       </c>
       <c r="F50">
-        <v>-4.057412234108799</v>
+        <v>-4.057412234109431</v>
       </c>
       <c r="G50">
-        <v>-0.7591398476533824</v>
+        <v>-0.7591398476533775</v>
       </c>
       <c r="H50">
-        <v>-0.3261023175185473</v>
+        <v>-0.3261023175186055</v>
       </c>
       <c r="I50">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J50" t="s">
         <v>356</v>
@@ -10921,16 +10921,16 @@
         <v>-0.0974091110819693</v>
       </c>
       <c r="F51">
-        <v>-4.341058248380718</v>
+        <v>-4.341058248381309</v>
       </c>
       <c r="G51">
-        <v>-0.4447954294995391</v>
+        <v>-0.4447954294995635</v>
       </c>
       <c r="H51">
-        <v>-0.2631252543186456</v>
+        <v>-0.2631252543187127</v>
       </c>
       <c r="I51">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J51" t="s">
         <v>363</v>
@@ -10965,16 +10965,16 @@
         <v>-0.0937948587991926</v>
       </c>
       <c r="F52">
-        <v>-4.285418671505597</v>
+        <v>-4.285418671506046</v>
       </c>
       <c r="G52">
-        <v>-0.5446998590969407</v>
+        <v>-0.5446998590970207</v>
       </c>
       <c r="H52">
-        <v>-0.231055153871539</v>
+        <v>-0.2310551538716933</v>
       </c>
       <c r="I52">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J52" t="s">
         <v>370</v>
@@ -11009,16 +11009,16 @@
         <v>-0.0589611591714685</v>
       </c>
       <c r="F53">
-        <v>-3.842254825782977</v>
+        <v>-3.842254825783537</v>
       </c>
       <c r="G53">
-        <v>-0.5016174053061189</v>
+        <v>-0.5016174053061238</v>
       </c>
       <c r="H53">
-        <v>-0.5980024857235635</v>
+        <v>-0.598002485723682</v>
       </c>
       <c r="I53">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J53" t="s">
         <v>377</v>
@@ -11053,16 +11053,16 @@
         <v>-0.0558324786773984</v>
       </c>
       <c r="F54">
-        <v>-4.1094395984704</v>
+        <v>-4.109439598471023</v>
       </c>
       <c r="G54">
-        <v>-0.006897302026347862</v>
+        <v>-0.006897302026323437</v>
       </c>
       <c r="H54">
-        <v>-0.7461745396217647</v>
+        <v>-0.7461745396218401</v>
       </c>
       <c r="I54">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J54" t="s">
         <v>384</v>
@@ -11097,16 +11097,16 @@
         <v>-0.0529082113950267</v>
       </c>
       <c r="F55">
-        <v>-3.949290358272369</v>
+        <v>-3.949290358272991</v>
       </c>
       <c r="G55">
-        <v>-0.0151455442734596</v>
+        <v>-0.01514554427343651</v>
       </c>
       <c r="H55">
-        <v>-0.6383582072087886</v>
+        <v>-0.6383582072088682</v>
       </c>
       <c r="I55">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J55" t="s">
         <v>391</v>
@@ -11141,16 +11141,16 @@
         <v>-0.0133189733864232</v>
       </c>
       <c r="F56">
-        <v>-3.4753126505816</v>
+        <v>-3.475312650582097</v>
       </c>
       <c r="G56">
-        <v>-1.02266664450105</v>
+        <v>-1.022666644501106</v>
       </c>
       <c r="H56">
-        <v>-0.4563786268908574</v>
+        <v>-0.4563786268909856</v>
       </c>
       <c r="I56">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J56" t="s">
         <v>398</v>
@@ -11185,16 +11185,16 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>-4.011924365327024</v>
+        <v>-4.011924365327615</v>
       </c>
       <c r="G57">
-        <v>-0.2170005175213139</v>
+        <v>-0.2170005175213143</v>
       </c>
       <c r="H57">
-        <v>-0.8070844139307382</v>
+        <v>-0.8070844139308306</v>
       </c>
       <c r="I57">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J57" t="s">
         <v>405</v>
@@ -11229,16 +11229,16 @@
         <v>0.1594150996807537</v>
       </c>
       <c r="F58">
-        <v>-4.234332783541925</v>
+        <v>-4.234332783542538</v>
       </c>
       <c r="G58">
-        <v>-0.5219079436724314</v>
+        <v>-0.5219079436724452</v>
       </c>
       <c r="H58">
-        <v>-0.1460057700544888</v>
+        <v>-0.1460057700545368</v>
       </c>
       <c r="I58">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J58" t="s">
         <v>411</v>
@@ -11273,16 +11273,16 @@
         <v>0.1675990426546959</v>
       </c>
       <c r="F59">
-        <v>-3.658321318635597</v>
+        <v>-3.658321318636154</v>
       </c>
       <c r="G59">
-        <v>-0.1077756158564784</v>
+        <v>-0.1077756158565006</v>
       </c>
       <c r="H59">
-        <v>-0.8359496414535373</v>
+        <v>-0.8359496414536387</v>
       </c>
       <c r="I59">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J59" t="s">
         <v>418</v>
@@ -11317,16 +11317,16 @@
         <v>0.09801063165382121</v>
       </c>
       <c r="F60">
-        <v>-4.799693410164208</v>
+        <v>-4.799693410164527</v>
       </c>
       <c r="G60">
-        <v>0.79979546426314</v>
+        <v>0.7997954642628904</v>
       </c>
       <c r="H60">
-        <v>-1.11983770769871</v>
+        <v>-1.119837707698819</v>
       </c>
       <c r="I60">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J60" t="s">
         <v>425</v>
@@ -11361,16 +11361,16 @@
         <v>0.277006797251848</v>
       </c>
       <c r="F61">
-        <v>-3.990767359435632</v>
+        <v>-3.990767359436363</v>
       </c>
       <c r="G61">
-        <v>0.1907283084983566</v>
+        <v>0.1907283084984455</v>
       </c>
       <c r="H61">
-        <v>-1.13482866856358</v>
+        <v>-1.134828668563604</v>
       </c>
       <c r="I61">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J61" t="s">
         <v>432</v>
@@ -11405,16 +11405,16 @@
         <v>0.2126191251097753</v>
       </c>
       <c r="F62">
-        <v>-3.35882122262829</v>
+        <v>-3.358821222628893</v>
       </c>
       <c r="G62">
-        <v>-0.8176724171600727</v>
+        <v>-0.8176724171600473</v>
       </c>
       <c r="H62">
-        <v>-0.6435633968553631</v>
+        <v>-0.6435633968554609</v>
       </c>
       <c r="I62">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J62" t="s">
         <v>439</v>
@@ -11449,16 +11449,16 @@
         <v>0.2759783394108414</v>
       </c>
       <c r="F63">
-        <v>-2.7167400767781</v>
+        <v>-2.716740076778624</v>
       </c>
       <c r="G63">
-        <v>-0.7892654763136577</v>
+        <v>-0.7892654763138456</v>
       </c>
       <c r="H63">
-        <v>-1.198238163688908</v>
+        <v>-1.198238163688877</v>
       </c>
       <c r="I63">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J63" t="s">
         <v>446</v>
@@ -11493,16 +11493,16 @@
         <v>0.3359480904225796</v>
       </c>
       <c r="F64">
-        <v>-4.214055538604558</v>
+        <v>-4.214055538605049</v>
       </c>
       <c r="G64">
-        <v>-0.4572222980524834</v>
+        <v>-0.4572222980525655</v>
       </c>
       <c r="H64">
-        <v>-0.06714220019410355</v>
+        <v>-0.06714220019421147</v>
       </c>
       <c r="I64">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J64" t="s">
         <v>453</v>
@@ -11537,16 +11537,16 @@
         <v>0.3581254553855987</v>
       </c>
       <c r="F65">
-        <v>-3.222828686412379</v>
+        <v>-3.222828686412976</v>
       </c>
       <c r="G65">
-        <v>-1.362302170008808</v>
+        <v>-1.362302170008875</v>
       </c>
       <c r="H65">
-        <v>-0.04203222288010922</v>
+        <v>-0.04203222288011699</v>
       </c>
       <c r="I65">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J65" t="s">
         <v>460</v>
@@ -11581,16 +11581,16 @@
         <v>0.5096612923312198</v>
       </c>
       <c r="F66">
-        <v>-2.827044365682449</v>
+        <v>-2.827044365683047</v>
       </c>
       <c r="G66">
-        <v>-0.8594375059743613</v>
+        <v>-0.8594375059744195</v>
       </c>
       <c r="H66">
-        <v>-0.8197261872858745</v>
+        <v>-0.8197261872859011</v>
       </c>
       <c r="I66">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J66" t="s">
         <v>467</v>
@@ -11625,16 +11625,16 @@
         <v>0.5606068545679082</v>
       </c>
       <c r="F67">
-        <v>-4.222844983721471</v>
+        <v>-4.222844983722089</v>
       </c>
       <c r="G67">
-        <v>-0.2153928447427056</v>
+        <v>-0.2153928447427247</v>
       </c>
       <c r="H67">
-        <v>-0.2731654550080808</v>
+        <v>-0.2731654550081363</v>
       </c>
       <c r="I67">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J67" t="s">
         <v>474</v>
@@ -11669,16 +11669,16 @@
         <v>0.5650356173405527</v>
       </c>
       <c r="F68">
-        <v>-3.830954860043809</v>
+        <v>-3.830954860044399</v>
       </c>
       <c r="G68">
-        <v>0.2000032515550818</v>
+        <v>0.2000032515551018</v>
       </c>
       <c r="H68">
-        <v>-0.8167769778303473</v>
+        <v>-0.816776977830453</v>
       </c>
       <c r="I68">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J68" t="s">
         <v>481</v>
@@ -11713,16 +11713,16 @@
         <v>0.8026917544773513</v>
       </c>
       <c r="F69">
-        <v>-3.484644650830469</v>
+        <v>-3.484644650831037</v>
       </c>
       <c r="G69">
-        <v>0.276708279452393</v>
+        <v>0.2767082794523366</v>
       </c>
       <c r="H69">
-        <v>-0.956326160137607</v>
+        <v>-0.9563261601376479</v>
       </c>
       <c r="I69">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J69" t="s">
         <v>488</v>
@@ -11757,16 +11757,16 @@
         <v>1.022797264917702</v>
       </c>
       <c r="F70">
-        <v>-3.426499205063422</v>
+        <v>-3.426499205064008</v>
       </c>
       <c r="G70">
-        <v>0.4858569764469474</v>
+        <v>0.4858569764470242</v>
       </c>
       <c r="H70">
-        <v>-1.079052144014919</v>
+        <v>-1.079052144015078</v>
       </c>
       <c r="I70">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J70" t="s">
         <v>495</v>
@@ -11801,16 +11801,16 @@
         <v>0.3076488763264452</v>
       </c>
       <c r="F71">
-        <v>-4.253638992358336</v>
+        <v>-4.253638992358998</v>
       </c>
       <c r="G71">
-        <v>0.6149482718047006</v>
+        <v>0.6149482718047032</v>
       </c>
       <c r="H71">
-        <v>-0.933151041809404</v>
+        <v>-0.9331510418094331</v>
       </c>
       <c r="I71">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J71" t="s">
         <v>502</v>
@@ -11845,16 +11845,16 @@
         <v>1.1567900398418</v>
       </c>
       <c r="F72">
-        <v>-4.22519090551293</v>
+        <v>-4.225190905513527</v>
       </c>
       <c r="G72">
-        <v>0.09048046091053585</v>
+        <v>0.09048046091057715</v>
       </c>
       <c r="H72">
-        <v>0.3451252754479334</v>
+        <v>0.3451252754478265</v>
       </c>
       <c r="I72">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J72" t="s">
         <v>509</v>
@@ -11889,16 +11889,16 @@
         <v>1.146933626609135</v>
       </c>
       <c r="F73">
-        <v>-2.960053009252014</v>
+        <v>-2.960053009252593</v>
       </c>
       <c r="G73">
-        <v>-0.04867748658439419</v>
+        <v>-0.04867748658454829</v>
       </c>
       <c r="H73">
-        <v>-0.8570337906653162</v>
+        <v>-0.8570337906652747</v>
       </c>
       <c r="I73">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J73" t="s">
         <v>516</v>
@@ -11933,16 +11933,16 @@
         <v>2.124102462440832</v>
       </c>
       <c r="F74">
-        <v>-2.006399109334373</v>
+        <v>-2.006399109334677</v>
       </c>
       <c r="G74">
-        <v>-0.06985661181621872</v>
+        <v>-0.06985661181660285</v>
       </c>
       <c r="H74">
-        <v>-0.8160357842440827</v>
+        <v>-0.8160357842441024</v>
       </c>
       <c r="I74">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J74" t="s">
         <v>523</v>
@@ -11977,16 +11977,16 @@
         <v>1.12146706304357</v>
       </c>
       <c r="F75">
-        <v>-3.960310628905549</v>
+        <v>-3.960310628906139</v>
       </c>
       <c r="G75">
-        <v>0.9936423026776606</v>
+        <v>0.9936423026776011</v>
       </c>
       <c r="H75">
-        <v>-0.8920785683469054</v>
+        <v>-0.8920785683469367</v>
       </c>
       <c r="I75">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J75" t="s">
         <v>530</v>
@@ -12021,16 +12021,16 @@
         <v>2.677877305284354</v>
       </c>
       <c r="F76">
-        <v>-2.724354377676763</v>
+        <v>-2.724354377677139</v>
       </c>
       <c r="G76">
-        <v>1.091767922237624</v>
+        <v>1.091767922237374</v>
       </c>
       <c r="H76">
-        <v>-0.758909873222033</v>
+        <v>-0.7589098732221113</v>
       </c>
       <c r="I76">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J76" t="s">
         <v>537</v>
@@ -12065,16 +12065,16 @@
         <v>2.830112053855664</v>
       </c>
       <c r="F77">
-        <v>-3.033747687949618</v>
+        <v>-3.033747687950246</v>
       </c>
       <c r="G77">
-        <v>1.250152472583423</v>
+        <v>1.250152472583436</v>
       </c>
       <c r="H77">
-        <v>-0.5794977739983188</v>
+        <v>-0.5794977739983956</v>
       </c>
       <c r="I77">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J77" t="s">
         <v>544</v>
@@ -12109,16 +12109,16 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>-4.488358092251349</v>
+        <v>-4.488358092252047</v>
       </c>
       <c r="G78">
-        <v>-0.3431887104441764</v>
+        <v>-0.3431887104441698</v>
       </c>
       <c r="H78">
-        <v>-0.4454254203490051</v>
+        <v>-0.4454254203489973</v>
       </c>
       <c r="I78">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J78" t="s">
         <v>20</v>
@@ -12153,16 +12153,16 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>-5.133446980040365</v>
+        <v>-5.133446980040589</v>
       </c>
       <c r="G79">
-        <v>-0.2373910858889321</v>
+        <v>-0.2373910858892865</v>
       </c>
       <c r="H79">
-        <v>-0.5081944762137273</v>
+        <v>-0.5081944762137697</v>
       </c>
       <c r="I79">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J79" t="s">
         <v>20</v>
@@ -12197,16 +12197,16 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>-2.767733471568108</v>
+        <v>-2.767733471568537</v>
       </c>
       <c r="G80">
-        <v>0.5782625416267946</v>
+        <v>0.5782625416266067</v>
       </c>
       <c r="H80">
-        <v>-1.017957745002034</v>
+        <v>-1.017957745002013</v>
       </c>
       <c r="I80">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J80" t="s">
         <v>20</v>
@@ -12241,16 +12241,16 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>-3.445180480842279</v>
+        <v>-3.445180480842991</v>
       </c>
       <c r="G81">
-        <v>0.6873259879393583</v>
+        <v>0.6873259879394946</v>
       </c>
       <c r="H81">
-        <v>-0.9363968552394573</v>
+        <v>-0.9363968552395086</v>
       </c>
       <c r="I81">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J81" t="s">
         <v>20</v>
@@ -12285,16 +12285,16 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>-2.796974591321141</v>
+        <v>-2.796974591321565</v>
       </c>
       <c r="G82">
-        <v>0.1784154672185561</v>
+        <v>0.1784154672183735</v>
       </c>
       <c r="H82">
-        <v>-1.383524515688295</v>
+        <v>-1.383524515688263</v>
       </c>
       <c r="I82">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J82" t="s">
         <v>20</v>
@@ -12329,16 +12329,16 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>-3.387234170682549</v>
+        <v>-3.387234170683286</v>
       </c>
       <c r="G83">
-        <v>0.1831940836555339</v>
+        <v>0.1831940836556596</v>
       </c>
       <c r="H83">
-        <v>-1.30863622317039</v>
+        <v>-1.30863622317046</v>
       </c>
       <c r="I83">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J83" t="s">
         <v>20</v>
@@ -12373,16 +12373,16 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>-2.832259780710497</v>
+        <v>-2.832259780710912</v>
       </c>
       <c r="G84">
-        <v>0.1060012337903187</v>
+        <v>0.1060012337901304</v>
       </c>
       <c r="H84">
-        <v>-1.200145978587746</v>
+        <v>-1.200145978587724</v>
       </c>
       <c r="I84">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J84" t="s">
         <v>20</v>
@@ -12417,16 +12417,16 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>-3.437778419455841</v>
+        <v>-3.437778419456568</v>
       </c>
       <c r="G85">
-        <v>0.1266362553504732</v>
+        <v>0.1266362553506073</v>
       </c>
       <c r="H85">
-        <v>-1.131818776722236</v>
+        <v>-1.131818776722323</v>
       </c>
       <c r="I85">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J85" t="s">
         <v>20</v>
@@ -12461,16 +12461,16 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>-4.398802820095365</v>
+        <v>-4.398802820096103</v>
       </c>
       <c r="G86">
-        <v>-0.2446268896264741</v>
+        <v>-0.244626889626447</v>
       </c>
       <c r="H86">
-        <v>-1.556610679421521</v>
+        <v>-1.556610679421475</v>
       </c>
       <c r="I86">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J86" t="s">
         <v>20</v>
@@ -12505,16 +12505,16 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>-5.038220360175951</v>
+        <v>-5.038220360176179</v>
       </c>
       <c r="G87">
-        <v>-0.0218600258545818</v>
+        <v>-0.02186002585489444</v>
       </c>
       <c r="H87">
-        <v>-1.689042459960801</v>
+        <v>-1.689042459960924</v>
       </c>
       <c r="I87">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J87" t="s">
         <v>20</v>
@@ -12549,16 +12549,16 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>-4.536395545583838</v>
+        <v>-4.53639554558451</v>
       </c>
       <c r="G88">
-        <v>-0.6173810665431194</v>
+        <v>-0.6173810665431199</v>
       </c>
       <c r="H88">
-        <v>-0.8408846138604693</v>
+        <v>-0.8408846138604722</v>
       </c>
       <c r="I88">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J88" t="s">
         <v>20</v>
@@ -12593,16 +12593,16 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>-5.211541361250742</v>
+        <v>-5.211541361250956</v>
       </c>
       <c r="G89">
-        <v>-0.6338473067985748</v>
+        <v>-0.6338473067988963</v>
       </c>
       <c r="H89">
-        <v>-1.137181236456717</v>
+        <v>-1.137181236456882</v>
       </c>
       <c r="I89">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J89" t="s">
         <v>20</v>
@@ -12637,16 +12637,16 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>-3.672464760194392</v>
+        <v>-3.969953517447672</v>
       </c>
       <c r="G90">
-        <v>-3.363222021820726</v>
+        <v>-2.65303506845572</v>
       </c>
       <c r="H90">
-        <v>-0.4263394110149034</v>
+        <v>-0.4936202559857202</v>
       </c>
       <c r="I90">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J90" t="s">
         <v>20</v>
@@ -12681,16 +12681,16 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>-3.970725927059102</v>
+        <v>-4.558780830704332</v>
       </c>
       <c r="G91">
-        <v>1.898062155976403</v>
+        <v>-0.4945727845776613</v>
       </c>
       <c r="H91">
-        <v>-0.7553739955828218</v>
+        <v>-0.104583453409216</v>
       </c>
       <c r="I91">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J91" t="s">
         <v>20</v>
@@ -12725,16 +12725,16 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>-3.513010569615017</v>
+        <v>-3.803341995812148</v>
       </c>
       <c r="G92">
-        <v>0.1492266286647479</v>
+        <v>-0.3240175990856562</v>
       </c>
       <c r="H92">
-        <v>-1.773749662741607</v>
+        <v>-0.6878886231312393</v>
       </c>
       <c r="I92">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J92" t="s">
         <v>20</v>
@@ -12769,16 +12769,16 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>-3.537023151994993</v>
+        <v>-4.41875482982099</v>
       </c>
       <c r="G93">
-        <v>2.08644728098321</v>
+        <v>-0.4979844766402977</v>
       </c>
       <c r="H93">
-        <v>-0.5969643313844581</v>
+        <v>-0.1773534661681471</v>
       </c>
       <c r="I93">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J93" t="s">
         <v>20</v>
@@ -12813,16 +12813,16 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>-3.43810559017329</v>
+        <v>-3.532261798282767</v>
       </c>
       <c r="G94">
-        <v>-0.7217148707767014</v>
+        <v>-0.4004747635957435</v>
       </c>
       <c r="H94">
-        <v>-1.734331510304765</v>
+        <v>-0.69275415845573</v>
       </c>
       <c r="I94">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J94" t="s">
         <v>20</v>
@@ -12857,16 +12857,16 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>-3.884098119269648</v>
+        <v>-2.747402642891176</v>
       </c>
       <c r="G95">
-        <v>2.4520646446618</v>
+        <v>0.8291203505542408</v>
       </c>
       <c r="H95">
-        <v>-1.928134120919649</v>
+        <v>-0.6662984035623072</v>
       </c>
       <c r="I95">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J95" t="s">
         <v>20</v>
@@ -12901,16 +12901,16 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>-3.701756562115722</v>
+        <v>-3.732282187917938</v>
       </c>
       <c r="G96">
-        <v>-0.1543549048661386</v>
+        <v>0.7723478578017082</v>
       </c>
       <c r="H96">
-        <v>-0.8421604926367887</v>
+        <v>-1.307277826330052</v>
       </c>
       <c r="I96">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J96" t="s">
         <v>20</v>
@@ -12945,16 +12945,16 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>-3.943074888928174</v>
+        <v>-4.43571686057496</v>
       </c>
       <c r="G97">
-        <v>0.8357596127273272</v>
+        <v>-0.09868238117602202</v>
       </c>
       <c r="H97">
-        <v>-1.138708648390547</v>
+        <v>-0.8538196146537914</v>
       </c>
       <c r="I97">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J97" t="s">
         <v>20</v>
@@ -12989,16 +12989,16 @@
         <v>0</v>
       </c>
       <c r="F98">
-        <v>-3.787668691807931</v>
+        <v>-5.284425845086288</v>
       </c>
       <c r="G98">
-        <v>-1.626304700363878</v>
+        <v>0.6740965372852457</v>
       </c>
       <c r="H98">
-        <v>-0.4979893003252823</v>
+        <v>-1.215745035787215</v>
       </c>
       <c r="I98">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J98" t="s">
         <v>20</v>
@@ -13033,16 +13033,16 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>-2.941368828543497</v>
+        <v>-4.68194433519783</v>
       </c>
       <c r="G99">
-        <v>1.799718315215329</v>
+        <v>-0.345886426283414</v>
       </c>
       <c r="H99">
-        <v>-1.529614537401977</v>
+        <v>-0.9379658688864722</v>
       </c>
       <c r="I99">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J99" t="s">
         <v>20</v>
@@ -13077,16 +13077,16 @@
         <v>0</v>
       </c>
       <c r="F100">
-        <v>-3.791341526545018</v>
+        <v>-5.076214861613411</v>
       </c>
       <c r="G100">
-        <v>-0.6830557479192394</v>
+        <v>0.6508382355622677</v>
       </c>
       <c r="H100">
-        <v>-0.7550326834975127</v>
+        <v>-1.80387791040857</v>
       </c>
       <c r="I100">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J100" t="s">
         <v>20</v>
@@ -13121,16 +13121,16 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>-3.802398071934265</v>
+        <v>-4.401228414124458</v>
       </c>
       <c r="G101">
-        <v>-0.3612640597405843</v>
+        <v>-0.8085762001202559</v>
       </c>
       <c r="H101">
-        <v>-1.038439914996529</v>
+        <v>-1.580170452356592</v>
       </c>
       <c r="I101">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J101" t="s">
         <v>20</v>
@@ -13165,16 +13165,16 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>-2.777401550233957</v>
+        <v>-2.777401550234555</v>
       </c>
       <c r="G102">
-        <v>-1.495073686326927</v>
+        <v>-1.495073686327352</v>
       </c>
       <c r="H102">
-        <v>0.01399818551633374</v>
+        <v>0.01399818551624825</v>
       </c>
       <c r="I102">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J102" t="s">
         <v>20</v>
@@ -13209,16 +13209,16 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>-4.342285739110191</v>
+        <v>-4.342285739110703</v>
       </c>
       <c r="G103">
-        <v>-3.993770333417771</v>
+        <v>-3.993770333417567</v>
       </c>
       <c r="H103">
-        <v>-0.4704128692121394</v>
+        <v>-0.4704128692121304</v>
       </c>
       <c r="I103">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J103" t="s">
         <v>20</v>
@@ -13253,16 +13253,16 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>-3.534529922547725</v>
+        <v>-3.53452992254851</v>
       </c>
       <c r="G104">
-        <v>2.54136750982247</v>
+        <v>2.541367509822773</v>
       </c>
       <c r="H104">
-        <v>-0.3309398255065683</v>
+        <v>-0.3309398255066499</v>
       </c>
       <c r="I104">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J104" t="s">
         <v>20</v>
@@ -13297,16 +13297,16 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>-1.497637215917767</v>
+        <v>-1.497637215918012</v>
       </c>
       <c r="G105">
-        <v>-1.465618322495015</v>
+        <v>-1.465618322495517</v>
       </c>
       <c r="H105">
-        <v>-0.227145840411053</v>
+        <v>-0.2271458404111766</v>
       </c>
       <c r="I105">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J105" t="s">
         <v>20</v>
@@ -13341,16 +13341,16 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>-3.069641381645387</v>
+        <v>-3.069641381646133</v>
       </c>
       <c r="G106">
-        <v>2.86965063646562</v>
+        <v>2.869650636465834</v>
       </c>
       <c r="H106">
-        <v>-0.4093291929832558</v>
+        <v>-0.4093291929833756</v>
       </c>
       <c r="I106">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J106" t="s">
         <v>20</v>
@@ -13385,16 +13385,16 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>-1.58514242276312</v>
+        <v>-1.585142422763425</v>
       </c>
       <c r="G107">
-        <v>-0.9075027717295097</v>
+        <v>-0.9075027717298672</v>
       </c>
       <c r="H107">
-        <v>-0.1860912247646963</v>
+        <v>-0.1860912247647997</v>
       </c>
       <c r="I107">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J107" t="s">
         <v>20</v>
@@ -13429,16 +13429,16 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>-3.124702260428205</v>
+        <v>-3.124702260428947</v>
       </c>
       <c r="G108">
-        <v>1.890108224953531</v>
+        <v>1.890108224953763</v>
       </c>
       <c r="H108">
-        <v>-0.508634602008301</v>
+        <v>-0.5086346020084236</v>
       </c>
       <c r="I108">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J108" t="s">
         <v>20</v>
@@ -13473,16 +13473,16 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <v>-1.510757240813364</v>
+        <v>-1.510757240813685</v>
       </c>
       <c r="G109">
-        <v>-1.943950662268463</v>
+        <v>-1.943950662268832</v>
       </c>
       <c r="H109">
-        <v>-0.2532958778619915</v>
+        <v>-0.2532958778621118</v>
       </c>
       <c r="I109">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J109" t="s">
         <v>20</v>
@@ -13517,16 +13517,16 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>-3.44501040392379</v>
+        <v>-3.445010403923983</v>
       </c>
       <c r="G110">
-        <v>1.1430316645698</v>
+        <v>1.143031664569606</v>
       </c>
       <c r="H110">
-        <v>-0.2988605043228511</v>
+        <v>-0.2988605043229288</v>
       </c>
       <c r="I110">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J110" t="s">
         <v>20</v>
@@ -13561,16 +13561,16 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>-3.822161027375655</v>
+        <v>-3.822161027376205</v>
       </c>
       <c r="G111">
-        <v>-1.054564552699147</v>
+        <v>-1.054564552699038</v>
       </c>
       <c r="H111">
-        <v>-0.4079254548243557</v>
+        <v>-0.407925454824479</v>
       </c>
       <c r="I111">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J111" t="s">
         <v>20</v>
@@ -13605,16 +13605,16 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <v>-2.831180847048642</v>
+        <v>-2.831180847049152</v>
       </c>
       <c r="G112">
-        <v>1.275616760423315</v>
+        <v>1.275616760422946</v>
       </c>
       <c r="H112">
-        <v>0.34674010869587</v>
+        <v>0.3467401086958092</v>
       </c>
       <c r="I112">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J112" t="s">
         <v>20</v>
@@ -13649,16 +13649,16 @@
         <v>0</v>
       </c>
       <c r="F113">
-        <v>-4.558115785213932</v>
+        <v>-4.558115785214436</v>
       </c>
       <c r="G113">
-        <v>-2.455196566157746</v>
+        <v>-2.455196566157593</v>
       </c>
       <c r="H113">
-        <v>0.4165672558539978</v>
+        <v>0.4165672558538913</v>
       </c>
       <c r="I113">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J113" t="s">
         <v>20</v>
@@ -13693,16 +13693,16 @@
         <v>0</v>
       </c>
       <c r="F114">
-        <v>-2.85995290177814</v>
+        <v>-2.859952901778767</v>
       </c>
       <c r="G114">
-        <v>-2.686742704939142</v>
+        <v>-2.686742704939153</v>
       </c>
       <c r="H114">
-        <v>-0.1657775104643768</v>
+        <v>-0.1657775104643303</v>
       </c>
       <c r="I114">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J114" t="s">
         <v>20</v>
@@ -13737,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <v>-4.368224179472984</v>
+        <v>-4.368224179473309</v>
       </c>
       <c r="G115">
-        <v>2.108587764289995</v>
+        <v>2.108587764289765</v>
       </c>
       <c r="H115">
-        <v>0.2453333474696504</v>
+        <v>0.2453333474695866</v>
       </c>
       <c r="I115">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J115" t="s">
         <v>20</v>
@@ -13781,16 +13781,16 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>-1.803010771507924</v>
+        <v>-1.80301077150843</v>
       </c>
       <c r="G116">
-        <v>-0.634740022992993</v>
+        <v>-0.6347400229931035</v>
       </c>
       <c r="H116">
-        <v>0.146529806123796</v>
+        <v>0.1465298061237958</v>
       </c>
       <c r="I116">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J116" t="s">
         <v>20</v>
@@ -13825,16 +13825,16 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>0.1669682422771432</v>
+        <v>0.1669682422766665</v>
       </c>
       <c r="G117">
-        <v>0.2767694946796774</v>
+        <v>0.276769494679621</v>
       </c>
       <c r="H117">
-        <v>-0.1675974659301726</v>
+        <v>-0.167597465930209</v>
       </c>
       <c r="I117">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J117" t="s">
         <v>20</v>
@@ -13869,16 +13869,16 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>-1.681220033422624</v>
+        <v>-1.681220033423109</v>
       </c>
       <c r="G118">
-        <v>-0.5758132006824144</v>
+        <v>-0.5758132006825927</v>
       </c>
       <c r="H118">
-        <v>0.154673414529034</v>
+        <v>0.1546734145290335</v>
       </c>
       <c r="I118">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J118" t="s">
         <v>20</v>
@@ -13913,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>0.2178021707978147</v>
+        <v>0.2178021707973087</v>
       </c>
       <c r="G119">
-        <v>0.8720036746910748</v>
+        <v>0.8720036746910402</v>
       </c>
       <c r="H119">
-        <v>-0.2051755604251885</v>
+        <v>-0.2051755604252286</v>
       </c>
       <c r="I119">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J119" t="s">
         <v>20</v>
@@ -13957,16 +13957,16 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>-1.859209687183875</v>
+        <v>-1.859209687184335</v>
       </c>
       <c r="G120">
-        <v>-0.4316621861878623</v>
+        <v>-0.4316621861880362</v>
       </c>
       <c r="H120">
-        <v>0.2343470766042101</v>
+        <v>0.2343470766042052</v>
       </c>
       <c r="I120">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J120" t="s">
         <v>20</v>
@@ -14001,16 +14001,16 @@
         <v>0</v>
       </c>
       <c r="F121">
-        <v>0.141893767769586</v>
+        <v>0.1418937677690885</v>
       </c>
       <c r="G121">
-        <v>0.3779516418147677</v>
+        <v>0.3779516418147564</v>
       </c>
       <c r="H121">
-        <v>-0.2954321121017278</v>
+        <v>-0.2954321121017913</v>
       </c>
       <c r="I121">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J121" t="s">
         <v>20</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>-2.329010364925044</v>
+        <v>-2.329010364925682</v>
       </c>
       <c r="G122">
-        <v>-2.406388326944952</v>
+        <v>-2.406388326944989</v>
       </c>
       <c r="H122">
-        <v>-0.1959976760845075</v>
+        <v>-0.1959976760844438</v>
       </c>
       <c r="I122">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J122" t="s">
         <v>20</v>
@@ -14089,16 +14089,16 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>-4.262169338302774</v>
+        <v>-4.262169338303054</v>
       </c>
       <c r="G123">
-        <v>2.270092379597599</v>
+        <v>2.270092379597339</v>
       </c>
       <c r="H123">
-        <v>0.2754720852893908</v>
+        <v>0.2754720852893089</v>
       </c>
       <c r="I123">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J123" t="s">
         <v>20</v>
@@ -14133,16 +14133,16 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <v>-2.647760432669218</v>
+        <v>-2.647760432669849</v>
       </c>
       <c r="G124">
-        <v>-2.109463286105123</v>
+        <v>-2.109463286105143</v>
       </c>
       <c r="H124">
-        <v>-0.2016010975187163</v>
+        <v>-0.2016010975186537</v>
       </c>
       <c r="I124">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J124" t="s">
         <v>20</v>
@@ -14177,16 +14177,16 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>-4.073880379221607</v>
+        <v>-4.073880379221914</v>
       </c>
       <c r="G125">
-        <v>0.823104926077725</v>
+        <v>0.823104926077511</v>
       </c>
       <c r="H125">
-        <v>0.3664440079923786</v>
+        <v>0.3664440079922875</v>
       </c>
       <c r="I125">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J125" t="s">
         <v>20</v>
@@ -14221,16 +14221,16 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>-2.073777083530469</v>
+        <v>-2.073777083530843</v>
       </c>
       <c r="G126">
-        <v>-0.7951488070773702</v>
+        <v>-0.7951488070777377</v>
       </c>
       <c r="H126">
-        <v>-0.6913692211744824</v>
+        <v>-0.6913692211759238</v>
       </c>
       <c r="I126">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J126" t="s">
         <v>20</v>
@@ -14265,16 +14265,16 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>-5.587871673466219</v>
+        <v>-5.587871673466808</v>
       </c>
       <c r="G127">
-        <v>-1.70342091034673</v>
+        <v>-1.703420910346568</v>
       </c>
       <c r="H127">
-        <v>-3.141457586618843</v>
+        <v>-3.141457586618221</v>
       </c>
       <c r="I127">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J127" t="s">
         <v>20</v>
@@ -14309,16 +14309,16 @@
         <v>0</v>
       </c>
       <c r="F128">
-        <v>-1.962799232129374</v>
+        <v>-1.962799232129703</v>
       </c>
       <c r="G128">
-        <v>-1.381855138486607</v>
+        <v>-1.381855138486825</v>
       </c>
       <c r="H128">
-        <v>-1.300692162495309</v>
+        <v>-1.300692162496271</v>
       </c>
       <c r="I128">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J128" t="s">
         <v>20</v>
@@ -14353,16 +14353,16 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <v>-4.316774444204796</v>
+        <v>-4.316774444205256</v>
       </c>
       <c r="G129">
-        <v>-0.3561450649741418</v>
+        <v>-0.3561450649740632</v>
       </c>
       <c r="H129">
-        <v>-2.03400958633688</v>
+        <v>-2.034009586336521</v>
       </c>
       <c r="I129">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J129" t="s">
         <v>20</v>
@@ -14397,16 +14397,16 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <v>-2.024197465528897</v>
+        <v>-2.024197465529382</v>
       </c>
       <c r="G130">
-        <v>-1.921779302173815</v>
+        <v>-1.921779302173916</v>
       </c>
       <c r="H130">
-        <v>-1.371140838784975</v>
+        <v>-1.371140838785354</v>
       </c>
       <c r="I130">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J130" t="s">
         <v>20</v>
@@ -14441,16 +14441,16 @@
         <v>0</v>
       </c>
       <c r="F131">
-        <v>-2.305793427329852</v>
+        <v>-2.305793427330187</v>
       </c>
       <c r="G131">
-        <v>4.272805672605148</v>
+        <v>4.272805672605094</v>
       </c>
       <c r="H131">
-        <v>0.09647420277944829</v>
+        <v>0.09647420277968821</v>
       </c>
       <c r="I131">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J131" t="s">
         <v>20</v>
@@ -14485,16 +14485,16 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>-2.004806879875362</v>
+        <v>-2.00480687987582</v>
       </c>
       <c r="G132">
-        <v>1.289241126405266</v>
+        <v>1.289241126405068</v>
       </c>
       <c r="H132">
-        <v>-1.86870990299259</v>
+        <v>-1.868709902992966</v>
       </c>
       <c r="I132">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J132" t="s">
         <v>20</v>
@@ -14529,16 +14529,16 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>-3.168526446575584</v>
+        <v>-3.168526446575948</v>
       </c>
       <c r="G133">
-        <v>3.615791675779524</v>
+        <v>3.615791675779396</v>
       </c>
       <c r="H133">
-        <v>-0.1611610678672885</v>
+        <v>-0.1611610678671484</v>
       </c>
       <c r="I133">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J133" t="s">
         <v>20</v>
@@ -14573,16 +14573,16 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>-2.343114972996503</v>
+        <v>-2.343114972996951</v>
       </c>
       <c r="G134">
-        <v>-1.073533595520592</v>
+        <v>-1.073533595520675</v>
       </c>
       <c r="H134">
-        <v>-0.6115606508512914</v>
+        <v>-0.6115606508514918</v>
       </c>
       <c r="I134">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J134" t="s">
         <v>20</v>
@@ -14617,16 +14617,16 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>-3.638418860664346</v>
+        <v>-3.638418860664845</v>
       </c>
       <c r="G135">
-        <v>0.6819990596400767</v>
+        <v>0.6819990596399843</v>
       </c>
       <c r="H135">
-        <v>-0.1930811657805974</v>
+        <v>-0.1930811657805896</v>
       </c>
       <c r="I135">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J135" t="s">
         <v>20</v>
@@ -14661,16 +14661,16 @@
         <v>0</v>
       </c>
       <c r="F136">
-        <v>-2.369573999443684</v>
+        <v>-2.369573999444136</v>
       </c>
       <c r="G136">
-        <v>1.606657683660859</v>
+        <v>1.606657683660626</v>
       </c>
       <c r="H136">
-        <v>-1.510661819024119</v>
+        <v>-1.510661819024379</v>
       </c>
       <c r="I136">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J136" t="s">
         <v>20</v>
@@ -14705,16 +14705,16 @@
         <v>0</v>
       </c>
       <c r="F137">
-        <v>-4.200374193202034</v>
+        <v>-4.20037419320263</v>
       </c>
       <c r="G137">
-        <v>1.554142364068406</v>
+        <v>1.554142364068396</v>
       </c>
       <c r="H137">
-        <v>-0.6227904124697978</v>
+        <v>-0.6227904124697095</v>
       </c>
       <c r="I137">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J137" t="s">
         <v>20</v>
@@ -14749,16 +14749,16 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <v>-3.931270852348119</v>
+        <v>-3.931270852348737</v>
       </c>
       <c r="G138">
-        <v>-1.05173391606073</v>
+        <v>-1.051733916060643</v>
       </c>
       <c r="H138">
-        <v>-0.6479781312879646</v>
+        <v>-0.6479781312883488</v>
       </c>
       <c r="I138">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J138" t="s">
         <v>20</v>
@@ -14793,16 +14793,16 @@
         <v>0</v>
       </c>
       <c r="F139">
-        <v>-3.367223602676734</v>
+        <v>-3.367223602677033</v>
       </c>
       <c r="G139">
-        <v>0.1472180990959182</v>
+        <v>0.1472180990956646</v>
       </c>
       <c r="H139">
-        <v>-0.5061747832928335</v>
+        <v>-0.5061747832927563</v>
       </c>
       <c r="I139">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J139" t="s">
         <v>20</v>
@@ -14837,16 +14837,16 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <v>-3.041243159901703</v>
+        <v>-3.041243159902084</v>
       </c>
       <c r="G140">
-        <v>-0.6814507587092458</v>
+        <v>-0.6814507587092782</v>
       </c>
       <c r="H140">
-        <v>-0.6179768399485855</v>
+        <v>-0.617976839949</v>
       </c>
       <c r="I140">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J140" t="s">
         <v>20</v>
@@ -14881,16 +14881,16 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>-2.032354666769167</v>
+        <v>-2.032354666769602</v>
       </c>
       <c r="G141">
-        <v>-2.339731164078317</v>
+        <v>-2.339731164078389</v>
       </c>
       <c r="H141">
-        <v>-0.3438505220509784</v>
+        <v>-0.3438505220510205</v>
       </c>
       <c r="I141">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J141" t="s">
         <v>20</v>
@@ -14925,16 +14925,16 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>-4.162926886211077</v>
+        <v>-4.162926886211674</v>
       </c>
       <c r="G142">
-        <v>-1.274196785078372</v>
+        <v>-1.27419678507837</v>
       </c>
       <c r="H142">
-        <v>-0.4631110992463589</v>
+        <v>-0.4631110992464972</v>
       </c>
       <c r="I142">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J142" t="s">
         <v>20</v>
@@ -14969,16 +14969,16 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>-4.101493817310574</v>
+        <v>-4.101493817311243</v>
       </c>
       <c r="G143">
-        <v>-0.386123633425715</v>
+        <v>-0.386123633425635</v>
       </c>
       <c r="H143">
-        <v>-0.4167219997860911</v>
+        <v>-0.4167219997861711</v>
       </c>
       <c r="I143">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J143" t="s">
         <v>20</v>
@@ -15013,16 +15013,16 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>-2.967797216448612</v>
+        <v>-2.967797216448856</v>
       </c>
       <c r="G144">
-        <v>0.4507987957647401</v>
+        <v>0.4507987957644057</v>
       </c>
       <c r="H144">
-        <v>-0.257844339142213</v>
+        <v>-0.2578443391422287</v>
       </c>
       <c r="I144">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J144" t="s">
         <v>20</v>
@@ -15057,16 +15057,16 @@
         <v>0</v>
       </c>
       <c r="F145">
-        <v>-3.24624520664189</v>
+        <v>-3.24624520664214</v>
       </c>
       <c r="G145">
-        <v>1.408010740349142</v>
+        <v>1.408010740348834</v>
       </c>
       <c r="H145">
-        <v>-0.489938519639966</v>
+        <v>-0.4899385196398983</v>
       </c>
       <c r="I145">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J145" t="s">
         <v>20</v>
@@ -15101,16 +15101,16 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>-2.931059227244876</v>
+        <v>-2.931059227245285</v>
       </c>
       <c r="G146">
-        <v>-1.279078644178409</v>
+        <v>-1.279078644178466</v>
       </c>
       <c r="H146">
-        <v>-0.3649468486733784</v>
+        <v>-0.3649468486735982</v>
       </c>
       <c r="I146">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J146" t="s">
         <v>20</v>
@@ -15145,16 +15145,16 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <v>-3.041913389758683</v>
+        <v>-3.041913389759152</v>
       </c>
       <c r="G147">
-        <v>0.294040499087763</v>
+        <v>0.2940404990877132</v>
       </c>
       <c r="H147">
-        <v>-0.8020153793669583</v>
+        <v>-0.8020153793671325</v>
       </c>
       <c r="I147">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J147" t="s">
         <v>20</v>
@@ -15189,16 +15189,16 @@
         <v>0</v>
       </c>
       <c r="F148">
-        <v>-1.963188747526794</v>
+        <v>-1.963188747527204</v>
       </c>
       <c r="G148">
-        <v>1.384212862591798</v>
+        <v>1.384212862591565</v>
       </c>
       <c r="H148">
-        <v>-0.565129274400223</v>
+        <v>-0.565129274400172</v>
       </c>
       <c r="I148">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J148" t="s">
         <v>20</v>
@@ -15233,16 +15233,16 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>-1.757806157721685</v>
+        <v>-1.757806157722057</v>
       </c>
       <c r="G149">
-        <v>-1.670477918560803</v>
+        <v>-1.670477918560878</v>
       </c>
       <c r="H149">
-        <v>-0.1234197217866741</v>
+        <v>-0.1234197217866631</v>
       </c>
       <c r="I149">
-        <v>4.970536696747911</v>
+        <v>4.97053669674859</v>
       </c>
       <c r="J149" t="s">
         <v>20</v>
